--- a/research/traditional_assets/database/data/italy/italy_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_oilfield_svcs_equip.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bit_srs" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0288</v>
+        <v>0.07012</v>
+      </c>
+      <c r="E2">
+        <v>0.205</v>
       </c>
       <c r="G2">
-        <v>0.01257895949271936</v>
+        <v>-0.07027930477305953</v>
       </c>
       <c r="H2">
-        <v>0.01011772693655355</v>
+        <v>-0.07174550521933162</v>
       </c>
       <c r="I2">
-        <v>-0.07173947307799562</v>
+        <v>-0.006758200890834325</v>
       </c>
       <c r="J2">
-        <v>-0.07173947307799562</v>
+        <v>-0.005068650668125743</v>
       </c>
       <c r="K2">
-        <v>-1596.3</v>
+        <v>-1071.4</v>
       </c>
       <c r="L2">
-        <v>-0.09677008693121886</v>
+        <v>-0.0457984594208722</v>
       </c>
       <c r="M2">
-        <v>97.40000000000001</v>
+        <v>25.5</v>
       </c>
       <c r="N2">
-        <v>0.03668964478095454</v>
+        <v>0.007139057644390942</v>
       </c>
       <c r="O2">
-        <v>-0.06101609973062708</v>
+        <v>-0.02380063468359156</v>
       </c>
       <c r="P2">
-        <v>80</v>
+        <v>25.5</v>
       </c>
       <c r="Q2">
-        <v>0.03013523185294007</v>
+        <v>0.007139057644390942</v>
       </c>
       <c r="R2">
-        <v>-0.05011589300256844</v>
+        <v>-0.02380063468359156</v>
       </c>
       <c r="S2">
-        <v>17.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1786447638603696</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>753.6</v>
+        <v>710.4</v>
       </c>
       <c r="V2">
-        <v>0.2838738840546955</v>
+        <v>0.1988857470813853</v>
       </c>
       <c r="W2">
-        <v>-0.2783754408437553</v>
+        <v>-0.14246256249212</v>
       </c>
       <c r="X2">
-        <v>0.1653235078257924</v>
+        <v>0.1528189999303932</v>
       </c>
       <c r="Y2">
-        <v>-0.4436989486695477</v>
+        <v>-0.2952815624225131</v>
       </c>
       <c r="Z2">
-        <v>2.403129233862157</v>
+        <v>4.26256331766335</v>
       </c>
       <c r="AA2">
-        <v>-0.1240428733701308</v>
+        <v>0.01543592957039644</v>
       </c>
       <c r="AB2">
-        <v>0.08496726530898843</v>
+        <v>0.1293407837628233</v>
       </c>
       <c r="AC2">
-        <v>-0.2090101386791192</v>
+        <v>-0.1139048541924269</v>
       </c>
       <c r="AD2">
-        <v>3388.3</v>
+        <v>1052</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3388.3</v>
+        <v>1052</v>
       </c>
       <c r="AG2">
-        <v>2634.7</v>
+        <v>341.6</v>
       </c>
       <c r="AH2">
-        <v>0.5606983286447129</v>
+        <v>0.2275135707952162</v>
       </c>
       <c r="AI2">
-        <v>0.5382525814138205</v>
+        <v>0.2541185564520025</v>
       </c>
       <c r="AJ2">
-        <v>0.4981094263999699</v>
+        <v>0.0872875942251182</v>
       </c>
       <c r="AK2">
-        <v>0.475457465622406</v>
+        <v>0.09960926109523532</v>
       </c>
       <c r="AL2">
-        <v>135.6</v>
+        <v>171.2</v>
       </c>
       <c r="AM2">
-        <v>135.488</v>
+        <v>165.22</v>
       </c>
       <c r="AN2">
-        <v>-6.718818163791394</v>
+        <v>2.831763122476446</v>
       </c>
       <c r="AO2">
-        <v>-8.727138643067848</v>
+        <v>-0.9234813084112151</v>
       </c>
       <c r="AP2">
-        <v>-5.224469561768788</v>
+        <v>0.9195154777927319</v>
       </c>
       <c r="AQ2">
-        <v>-8.734352857817667</v>
+        <v>-0.9569059435903645</v>
       </c>
     </row>
     <row r="3">
@@ -719,25 +724,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0274</v>
+        <v>0.138</v>
+      </c>
+      <c r="E3">
+        <v>0.205</v>
       </c>
       <c r="G3">
-        <v>-0.01077521700089793</v>
+        <v>0.02099859042038639</v>
       </c>
       <c r="H3">
-        <v>-0.01077521700089793</v>
+        <v>0.02099859042038639</v>
       </c>
       <c r="I3">
-        <v>-0.005974259203831188</v>
+        <v>0.0694356153782372</v>
       </c>
       <c r="J3">
-        <v>-0.005974259203831188</v>
+        <v>0.0347178076891186</v>
       </c>
       <c r="K3">
-        <v>-158</v>
+        <v>383.8</v>
       </c>
       <c r="L3">
-        <v>-0.01891649206824304</v>
+        <v>0.02651944390702303</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,7 +754,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,79 +763,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>753.6</v>
+        <v>710.4</v>
       </c>
       <c r="V3">
-        <v>1.283160224757364</v>
+        <v>0.6083233430381915</v>
       </c>
       <c r="W3">
-        <v>-0.1518354795310398</v>
+        <v>0.440390131956397</v>
       </c>
       <c r="X3">
-        <v>0.2033904626942747</v>
+        <v>0.1653978723150483</v>
       </c>
       <c r="Y3">
-        <v>-0.3552259422253145</v>
+        <v>0.2749922596413487</v>
       </c>
       <c r="Z3">
-        <v>5.003294596861148</v>
+        <v>9.379998703739709</v>
       </c>
       <c r="AA3">
-        <v>-0.02989097879477657</v>
+        <v>0.325652991120617</v>
       </c>
       <c r="AB3">
-        <v>0.08390594288116821</v>
+        <v>0.129087805714215</v>
       </c>
       <c r="AC3">
-        <v>-0.1137969216759448</v>
+        <v>0.196565185406402</v>
       </c>
       <c r="AD3">
-        <v>1449.3</v>
+        <v>634.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1449.3</v>
+        <v>634.3</v>
       </c>
       <c r="AG3">
-        <v>695.6999999999999</v>
+        <v>-76.10000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.7116272218403221</v>
+        <v>0.3519782476000222</v>
       </c>
       <c r="AI3">
-        <v>0.6244829369183039</v>
+        <v>0.3616099424206146</v>
       </c>
       <c r="AJ3">
-        <v>0.542244738893219</v>
+        <v>-0.06970779518182654</v>
       </c>
       <c r="AK3">
-        <v>0.4439127105666156</v>
+        <v>-0.07291367251125806</v>
       </c>
       <c r="AL3">
-        <v>23.2</v>
+        <v>25.1</v>
       </c>
       <c r="AM3">
-        <v>23.088</v>
+        <v>25</v>
       </c>
       <c r="AN3">
-        <v>8.123878923766815</v>
+        <v>0.5355454238432961</v>
       </c>
       <c r="AO3">
-        <v>-2.150862068965517</v>
+        <v>40.03585657370517</v>
       </c>
       <c r="AP3">
-        <v>3.899663677130044</v>
+        <v>-0.0642519419115164</v>
       </c>
       <c r="AQ3">
-        <v>-2.161295911295911</v>
+        <v>40.196</v>
       </c>
     </row>
     <row r="4">
@@ -847,49 +855,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.08500000000000001</v>
+        <v>0.00224</v>
       </c>
       <c r="G4">
-        <v>0.03653310083135829</v>
+        <v>-0.2183513798282781</v>
       </c>
       <c r="H4">
-        <v>0.03154740707084351</v>
+        <v>-0.2221960678817226</v>
       </c>
       <c r="I4">
-        <v>-0.1391941841759483</v>
+        <v>-0.1303607057188334</v>
       </c>
       <c r="J4">
-        <v>-0.1391941841759483</v>
+        <v>-0.1303607057188334</v>
       </c>
       <c r="K4">
-        <v>-1438.3</v>
+        <v>-1455.2</v>
       </c>
       <c r="L4">
-        <v>-0.1766237274814878</v>
+        <v>-0.1631134126930751</v>
       </c>
       <c r="M4">
-        <v>97.40000000000001</v>
+        <v>25.5</v>
       </c>
       <c r="N4">
-        <v>0.04711231498500532</v>
+        <v>0.01060687991348114</v>
       </c>
       <c r="O4">
-        <v>-0.06771883473545158</v>
+        <v>-0.01752336448598131</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>25.5</v>
       </c>
       <c r="Q4">
-        <v>0.03869594659959369</v>
+        <v>0.01060687991348114</v>
       </c>
       <c r="R4">
-        <v>-0.05562121949523743</v>
+        <v>-0.01752336448598131</v>
       </c>
       <c r="S4">
-        <v>17.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.1786447638603696</v>
+        <v>0</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -898,67 +906,8779 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>-0.4049154021564708</v>
+        <v>-0.725315256940637</v>
       </c>
       <c r="X4">
-        <v>0.1272565529573101</v>
+        <v>0.140240127545738</v>
       </c>
       <c r="Y4">
-        <v>-0.5321719551137809</v>
+        <v>-0.865555384486375</v>
       </c>
       <c r="Z4">
-        <v>1.567556642091282</v>
+        <v>2.261272907003269</v>
       </c>
       <c r="AA4">
-        <v>-0.218194767945485</v>
+        <v>-0.2947811319798241</v>
       </c>
       <c r="AB4">
-        <v>0.08602858773680866</v>
+        <v>0.1295937618114316</v>
       </c>
       <c r="AC4">
-        <v>-0.3042233556822936</v>
+        <v>-0.4243748937912557</v>
       </c>
       <c r="AD4">
-        <v>1939</v>
+        <v>417.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1939</v>
+        <v>417.7</v>
       </c>
       <c r="AG4">
-        <v>1939</v>
+        <v>417.7</v>
       </c>
       <c r="AH4">
-        <v>0.4839756389776358</v>
+        <v>0.1480260826422851</v>
       </c>
       <c r="AI4">
-        <v>0.487896935232248</v>
+        <v>0.1750848807477889</v>
       </c>
       <c r="AJ4">
-        <v>0.4839756389776358</v>
+        <v>0.1480260826422851</v>
       </c>
       <c r="AK4">
-        <v>0.487896935232248</v>
+        <v>0.1750848807477889</v>
       </c>
       <c r="AL4">
-        <v>112.4</v>
+        <v>146.1</v>
       </c>
       <c r="AM4">
-        <v>112.4</v>
+        <v>140.22</v>
       </c>
       <c r="AN4">
-        <v>-2.840193349934085</v>
+        <v>-0.5138393406323041</v>
       </c>
       <c r="AO4">
-        <v>-10.08451957295374</v>
+        <v>-7.960301163586585</v>
       </c>
       <c r="AP4">
-        <v>-2.840193349934085</v>
+        <v>-0.5138393406323041</v>
       </c>
       <c r="AQ4">
-        <v>-10.08451957295374</v>
+        <v>-8.294109256882043</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Saras S.p.A. (BIT:SRS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BIT:SRS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oilfield Svcs/Equip.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.351978247600022</v>
+      </c>
+      <c r="F2">
+        <v>0.99</v>
+      </c>
+      <c r="G2">
+        <v>1167.8</v>
+      </c>
+      <c r="H2">
+        <v>75.7591200266218</v>
+      </c>
+      <c r="I2">
+        <v>1091.7</v>
+      </c>
+      <c r="J2">
+        <v>1149.43812002662</v>
+      </c>
+      <c r="K2">
+        <v>634.3</v>
+      </c>
+      <c r="L2">
+        <v>1784.079</v>
+      </c>
+      <c r="M2">
+        <v>0.129087805714215</v>
+      </c>
+      <c r="N2">
+        <v>0.104293485241295</v>
+      </c>
+      <c r="O2">
+        <v>0.0622378990825688</v>
+      </c>
+      <c r="P2">
+        <v>0.035948</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.165397872315048</v>
+      </c>
+      <c r="T2">
+        <v>6.8704965241295</v>
+      </c>
+      <c r="U2">
+        <v>1.30409909138963</v>
+      </c>
+      <c r="V2">
+        <v>70.3740834411159</v>
+      </c>
+      <c r="W2">
+        <v>11.79329454199752</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>1167.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.09707688100614176</v>
+      </c>
+      <c r="AC2">
+        <v>0.08189197247706423</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1184.4</v>
+      </c>
+      <c r="AH2">
+        <v>189.2</v>
+      </c>
+      <c r="AI2">
+        <v>97.60000000000002</v>
+      </c>
+      <c r="AJ2">
+        <v>634.3</v>
+      </c>
+      <c r="AK2">
+        <v>634.3</v>
+      </c>
+      <c r="AL2">
+        <v>25.1</v>
+      </c>
+      <c r="AM2">
+        <v>634.3</v>
+      </c>
+      <c r="AN2">
+        <v>710.4</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1284077718275119</v>
+      </c>
+      <c r="C2">
+        <v>1803.606112588916</v>
+      </c>
+      <c r="D2">
+        <v>1093.206112588916</v>
+      </c>
+      <c r="E2">
+        <v>-634.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>710.4</v>
+      </c>
+      <c r="H2">
+        <v>1167.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1184.4</v>
+      </c>
+      <c r="K2">
+        <v>189.2</v>
+      </c>
+      <c r="L2">
+        <v>995.2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>995.2</v>
+      </c>
+      <c r="O2">
+        <v>238.848</v>
+      </c>
+      <c r="P2">
+        <v>756.3520000000001</v>
+      </c>
+      <c r="Q2">
+        <v>945.5520000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1284077718275119</v>
+      </c>
+      <c r="T2">
+        <v>0.9230598562580796</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1281520331751259</v>
+      </c>
+      <c r="C3">
+        <v>1786.152588431381</v>
+      </c>
+      <c r="D3">
+        <v>1093.773588431381</v>
+      </c>
+      <c r="E3">
+        <v>-616.279</v>
+      </c>
+      <c r="F3">
+        <v>18.021</v>
+      </c>
+      <c r="G3">
+        <v>710.4</v>
+      </c>
+      <c r="H3">
+        <v>1167.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1184.4</v>
+      </c>
+      <c r="K3">
+        <v>189.2</v>
+      </c>
+      <c r="L3">
+        <v>995.2</v>
+      </c>
+      <c r="M3">
+        <v>0.8235597000000001</v>
+      </c>
+      <c r="N3">
+        <v>994.3764403</v>
+      </c>
+      <c r="O3">
+        <v>238.650345672</v>
+      </c>
+      <c r="P3">
+        <v>755.7260946280001</v>
+      </c>
+      <c r="Q3">
+        <v>944.9260946280001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1290956698738645</v>
+      </c>
+      <c r="T3">
+        <v>0.9301459723263236</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>1208.412699164371</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1278962945227398</v>
+      </c>
+      <c r="C4">
+        <v>1768.699653725511</v>
+      </c>
+      <c r="D4">
+        <v>1094.341653725511</v>
+      </c>
+      <c r="E4">
+        <v>-598.2579999999999</v>
+      </c>
+      <c r="F4">
+        <v>36.042</v>
+      </c>
+      <c r="G4">
+        <v>710.4</v>
+      </c>
+      <c r="H4">
+        <v>1167.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1184.4</v>
+      </c>
+      <c r="K4">
+        <v>189.2</v>
+      </c>
+      <c r="L4">
+        <v>995.2</v>
+      </c>
+      <c r="M4">
+        <v>1.6471194</v>
+      </c>
+      <c r="N4">
+        <v>993.5528806000001</v>
+      </c>
+      <c r="O4">
+        <v>238.452691344</v>
+      </c>
+      <c r="P4">
+        <v>755.100189256</v>
+      </c>
+      <c r="Q4">
+        <v>944.3001892560001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.129797606655857</v>
+      </c>
+      <c r="T4">
+        <v>0.9373767030082049</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>604.2063495821857</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1276405558703539</v>
+      </c>
+      <c r="C5">
+        <v>1751.2473093902</v>
+      </c>
+      <c r="D5">
+        <v>1094.910309390201</v>
+      </c>
+      <c r="E5">
+        <v>-580.237</v>
+      </c>
+      <c r="F5">
+        <v>54.063</v>
+      </c>
+      <c r="G5">
+        <v>710.4</v>
+      </c>
+      <c r="H5">
+        <v>1167.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1184.4</v>
+      </c>
+      <c r="K5">
+        <v>189.2</v>
+      </c>
+      <c r="L5">
+        <v>995.2</v>
+      </c>
+      <c r="M5">
+        <v>2.4706791</v>
+      </c>
+      <c r="N5">
+        <v>992.7293209000001</v>
+      </c>
+      <c r="O5">
+        <v>238.255037016</v>
+      </c>
+      <c r="P5">
+        <v>754.474283884</v>
+      </c>
+      <c r="Q5">
+        <v>943.674283884</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1305140163611895</v>
+      </c>
+      <c r="T5">
+        <v>0.9447565209206408</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>402.8042330547905</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1273848172179678</v>
+      </c>
+      <c r="C6">
+        <v>1733.795556346257</v>
+      </c>
+      <c r="D6">
+        <v>1095.479556346257</v>
+      </c>
+      <c r="E6">
+        <v>-562.2159999999999</v>
+      </c>
+      <c r="F6">
+        <v>72.084</v>
+      </c>
+      <c r="G6">
+        <v>710.4</v>
+      </c>
+      <c r="H6">
+        <v>1167.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1184.4</v>
+      </c>
+      <c r="K6">
+        <v>189.2</v>
+      </c>
+      <c r="L6">
+        <v>995.2</v>
+      </c>
+      <c r="M6">
+        <v>3.2942388</v>
+      </c>
+      <c r="N6">
+        <v>991.9057612</v>
+      </c>
+      <c r="O6">
+        <v>238.057382688</v>
+      </c>
+      <c r="P6">
+        <v>753.8483785120001</v>
+      </c>
+      <c r="Q6">
+        <v>943.048378512</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1312453512687164</v>
+      </c>
+      <c r="T6">
+        <v>0.9522900850395856</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>302.1031747910928</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1271290785655818</v>
+      </c>
+      <c r="C7">
+        <v>1716.3443955164</v>
+      </c>
+      <c r="D7">
+        <v>1096.0493955164</v>
+      </c>
+      <c r="E7">
+        <v>-544.1949999999999</v>
+      </c>
+      <c r="F7">
+        <v>90.105</v>
+      </c>
+      <c r="G7">
+        <v>710.4</v>
+      </c>
+      <c r="H7">
+        <v>1167.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1184.4</v>
+      </c>
+      <c r="K7">
+        <v>189.2</v>
+      </c>
+      <c r="L7">
+        <v>995.2</v>
+      </c>
+      <c r="M7">
+        <v>4.117798500000001</v>
+      </c>
+      <c r="N7">
+        <v>991.0822015</v>
+      </c>
+      <c r="O7">
+        <v>237.85972836</v>
+      </c>
+      <c r="P7">
+        <v>753.22247314</v>
+      </c>
+      <c r="Q7">
+        <v>942.42247314</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1319920827006124</v>
+      </c>
+      <c r="T7">
+        <v>0.9599822505084028</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>241.6825398328742</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1268733399131957</v>
+      </c>
+      <c r="C8">
+        <v>1698.893827825274</v>
+      </c>
+      <c r="D8">
+        <v>1096.619827825274</v>
+      </c>
+      <c r="E8">
+        <v>-526.174</v>
+      </c>
+      <c r="F8">
+        <v>108.126</v>
+      </c>
+      <c r="G8">
+        <v>710.4</v>
+      </c>
+      <c r="H8">
+        <v>1167.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1184.4</v>
+      </c>
+      <c r="K8">
+        <v>189.2</v>
+      </c>
+      <c r="L8">
+        <v>995.2</v>
+      </c>
+      <c r="M8">
+        <v>4.9413582</v>
+      </c>
+      <c r="N8">
+        <v>990.2586418000001</v>
+      </c>
+      <c r="O8">
+        <v>237.662074032</v>
+      </c>
+      <c r="P8">
+        <v>752.5965677680001</v>
+      </c>
+      <c r="Q8">
+        <v>941.7965677680002</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1327547020353146</v>
+      </c>
+      <c r="T8">
+        <v>0.9678380790723013</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>201.4021165273953</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1266176012608097</v>
+      </c>
+      <c r="C9">
+        <v>1681.443854199447</v>
+      </c>
+      <c r="D9">
+        <v>1097.190854199447</v>
+      </c>
+      <c r="E9">
+        <v>-508.153</v>
+      </c>
+      <c r="F9">
+        <v>126.147</v>
+      </c>
+      <c r="G9">
+        <v>710.4</v>
+      </c>
+      <c r="H9">
+        <v>1167.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1184.4</v>
+      </c>
+      <c r="K9">
+        <v>189.2</v>
+      </c>
+      <c r="L9">
+        <v>995.2</v>
+      </c>
+      <c r="M9">
+        <v>5.764917900000001</v>
+      </c>
+      <c r="N9">
+        <v>989.4350821</v>
+      </c>
+      <c r="O9">
+        <v>237.464419704</v>
+      </c>
+      <c r="P9">
+        <v>751.9706623960001</v>
+      </c>
+      <c r="Q9">
+        <v>941.1706623960001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1335337217858169</v>
+      </c>
+      <c r="T9">
+        <v>0.9758628501859611</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>172.6303855949102</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1263618626084237</v>
+      </c>
+      <c r="C10">
+        <v>1663.994475567419</v>
+      </c>
+      <c r="D10">
+        <v>1097.762475567419</v>
+      </c>
+      <c r="E10">
+        <v>-490.1319999999999</v>
+      </c>
+      <c r="F10">
+        <v>144.168</v>
+      </c>
+      <c r="G10">
+        <v>710.4</v>
+      </c>
+      <c r="H10">
+        <v>1167.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1184.4</v>
+      </c>
+      <c r="K10">
+        <v>189.2</v>
+      </c>
+      <c r="L10">
+        <v>995.2</v>
+      </c>
+      <c r="M10">
+        <v>6.588477600000001</v>
+      </c>
+      <c r="N10">
+        <v>988.6115224</v>
+      </c>
+      <c r="O10">
+        <v>237.266765376</v>
+      </c>
+      <c r="P10">
+        <v>751.344757024</v>
+      </c>
+      <c r="Q10">
+        <v>940.5447570240001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1343296767482866</v>
+      </c>
+      <c r="T10">
+        <v>0.98406207284557</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>151.0515873955464</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1261061239560377</v>
+      </c>
+      <c r="C11">
+        <v>1646.545692859625</v>
+      </c>
+      <c r="D11">
+        <v>1098.334692859625</v>
+      </c>
+      <c r="E11">
+        <v>-472.111</v>
+      </c>
+      <c r="F11">
+        <v>162.189</v>
+      </c>
+      <c r="G11">
+        <v>710.4</v>
+      </c>
+      <c r="H11">
+        <v>1167.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1184.4</v>
+      </c>
+      <c r="K11">
+        <v>189.2</v>
+      </c>
+      <c r="L11">
+        <v>995.2</v>
+      </c>
+      <c r="M11">
+        <v>7.412037300000001</v>
+      </c>
+      <c r="N11">
+        <v>987.7879627000001</v>
+      </c>
+      <c r="O11">
+        <v>237.069111048</v>
+      </c>
+      <c r="P11">
+        <v>750.718851652</v>
+      </c>
+      <c r="Q11">
+        <v>939.9188516520001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.135143125226415</v>
+      </c>
+      <c r="T11">
+        <v>0.9924414982009946</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>134.2680776849302</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1258503853036516</v>
+      </c>
+      <c r="C12">
+        <v>1629.097507008441</v>
+      </c>
+      <c r="D12">
+        <v>1098.907507008442</v>
+      </c>
+      <c r="E12">
+        <v>-454.0899999999999</v>
+      </c>
+      <c r="F12">
+        <v>180.21</v>
+      </c>
+      <c r="G12">
+        <v>710.4</v>
+      </c>
+      <c r="H12">
+        <v>1167.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1184.4</v>
+      </c>
+      <c r="K12">
+        <v>189.2</v>
+      </c>
+      <c r="L12">
+        <v>995.2</v>
+      </c>
+      <c r="M12">
+        <v>8.235597000000002</v>
+      </c>
+      <c r="N12">
+        <v>986.9644030000001</v>
+      </c>
+      <c r="O12">
+        <v>236.87145672</v>
+      </c>
+      <c r="P12">
+        <v>750.0929462800001</v>
+      </c>
+      <c r="Q12">
+        <v>939.29294628</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1359746503373907</v>
+      </c>
+      <c r="T12">
+        <v>1.001007133008762</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>120.8412699164371</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1255946466512656</v>
+      </c>
+      <c r="C13">
+        <v>1611.649918948192</v>
+      </c>
+      <c r="D13">
+        <v>1099.480918948192</v>
+      </c>
+      <c r="E13">
+        <v>-436.069</v>
+      </c>
+      <c r="F13">
+        <v>198.231</v>
+      </c>
+      <c r="G13">
+        <v>710.4</v>
+      </c>
+      <c r="H13">
+        <v>1167.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1184.4</v>
+      </c>
+      <c r="K13">
+        <v>189.2</v>
+      </c>
+      <c r="L13">
+        <v>995.2</v>
+      </c>
+      <c r="M13">
+        <v>9.059156700000001</v>
+      </c>
+      <c r="N13">
+        <v>986.1408433</v>
+      </c>
+      <c r="O13">
+        <v>236.673802392</v>
+      </c>
+      <c r="P13">
+        <v>749.4670409080001</v>
+      </c>
+      <c r="Q13">
+        <v>938.667040908</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1368248614059164</v>
+      </c>
+      <c r="T13">
+        <v>1.009765253991985</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>109.8556999240338</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1253389079988796</v>
+      </c>
+      <c r="C14">
+        <v>1594.20292961515</v>
+      </c>
+      <c r="D14">
+        <v>1100.05492961515</v>
+      </c>
+      <c r="E14">
+        <v>-418.048</v>
+      </c>
+      <c r="F14">
+        <v>216.252</v>
+      </c>
+      <c r="G14">
+        <v>710.4</v>
+      </c>
+      <c r="H14">
+        <v>1167.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1184.4</v>
+      </c>
+      <c r="K14">
+        <v>189.2</v>
+      </c>
+      <c r="L14">
+        <v>995.2</v>
+      </c>
+      <c r="M14">
+        <v>9.8827164</v>
+      </c>
+      <c r="N14">
+        <v>985.3172836</v>
+      </c>
+      <c r="O14">
+        <v>236.476148064</v>
+      </c>
+      <c r="P14">
+        <v>748.841135536</v>
+      </c>
+      <c r="Q14">
+        <v>938.041135536</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1376943954532722</v>
+      </c>
+      <c r="T14">
+        <v>1.018722423179371</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>100.7010582636976</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1250831693464936</v>
+      </c>
+      <c r="C15">
+        <v>1576.756539947545</v>
+      </c>
+      <c r="D15">
+        <v>1100.629539947545</v>
+      </c>
+      <c r="E15">
+        <v>-400.0269999999999</v>
+      </c>
+      <c r="F15">
+        <v>234.273</v>
+      </c>
+      <c r="G15">
+        <v>710.4</v>
+      </c>
+      <c r="H15">
+        <v>1167.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1184.4</v>
+      </c>
+      <c r="K15">
+        <v>189.2</v>
+      </c>
+      <c r="L15">
+        <v>995.2</v>
+      </c>
+      <c r="M15">
+        <v>10.7062761</v>
+      </c>
+      <c r="N15">
+        <v>984.4937239000001</v>
+      </c>
+      <c r="O15">
+        <v>236.278493736</v>
+      </c>
+      <c r="P15">
+        <v>748.2152301640001</v>
+      </c>
+      <c r="Q15">
+        <v>937.4152301640001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1385839187890731</v>
+      </c>
+      <c r="T15">
+        <v>1.027885504302101</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>92.95482301264396</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1248274306941075</v>
+      </c>
+      <c r="C16">
+        <v>1559.310750885568</v>
+      </c>
+      <c r="D16">
+        <v>1101.204750885568</v>
+      </c>
+      <c r="E16">
+        <v>-382.006</v>
+      </c>
+      <c r="F16">
+        <v>252.294</v>
+      </c>
+      <c r="G16">
+        <v>710.4</v>
+      </c>
+      <c r="H16">
+        <v>1167.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1184.4</v>
+      </c>
+      <c r="K16">
+        <v>189.2</v>
+      </c>
+      <c r="L16">
+        <v>995.2</v>
+      </c>
+      <c r="M16">
+        <v>11.5298358</v>
+      </c>
+      <c r="N16">
+        <v>983.6701642</v>
+      </c>
+      <c r="O16">
+        <v>236.080839408</v>
+      </c>
+      <c r="P16">
+        <v>747.5893247920001</v>
+      </c>
+      <c r="Q16">
+        <v>936.7893247920001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1394941287140785</v>
+      </c>
+      <c r="T16">
+        <v>1.037261680334661</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>86.31519279745508</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1245716920417215</v>
+      </c>
+      <c r="C17">
+        <v>1541.865563371377</v>
+      </c>
+      <c r="D17">
+        <v>1101.780563371377</v>
+      </c>
+      <c r="E17">
+        <v>-363.985</v>
+      </c>
+      <c r="F17">
+        <v>270.315</v>
+      </c>
+      <c r="G17">
+        <v>710.4</v>
+      </c>
+      <c r="H17">
+        <v>1167.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1184.4</v>
+      </c>
+      <c r="K17">
+        <v>189.2</v>
+      </c>
+      <c r="L17">
+        <v>995.2</v>
+      </c>
+      <c r="M17">
+        <v>12.3533955</v>
+      </c>
+      <c r="N17">
+        <v>982.8466045</v>
+      </c>
+      <c r="O17">
+        <v>235.88318508</v>
+      </c>
+      <c r="P17">
+        <v>746.96341942</v>
+      </c>
+      <c r="Q17">
+        <v>936.1634194200001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1404257553432017</v>
+      </c>
+      <c r="T17">
+        <v>1.046858472273869</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>80.56084661095809</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1243159533893354</v>
+      </c>
+      <c r="C18">
+        <v>1524.420978349103</v>
+      </c>
+      <c r="D18">
+        <v>1102.356978349103</v>
+      </c>
+      <c r="E18">
+        <v>-345.9639999999999</v>
+      </c>
+      <c r="F18">
+        <v>288.336</v>
+      </c>
+      <c r="G18">
+        <v>710.4</v>
+      </c>
+      <c r="H18">
+        <v>1167.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1184.4</v>
+      </c>
+      <c r="K18">
+        <v>189.2</v>
+      </c>
+      <c r="L18">
+        <v>995.2</v>
+      </c>
+      <c r="M18">
+        <v>13.1769552</v>
+      </c>
+      <c r="N18">
+        <v>982.0230448000001</v>
+      </c>
+      <c r="O18">
+        <v>235.685530752</v>
+      </c>
+      <c r="P18">
+        <v>746.3375140480001</v>
+      </c>
+      <c r="Q18">
+        <v>935.537514048</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1413795635587327</v>
+      </c>
+      <c r="T18">
+        <v>1.056683759259249</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>75.52579369777321</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1240602147369494</v>
+      </c>
+      <c r="C19">
+        <v>1506.97699676485</v>
+      </c>
+      <c r="D19">
+        <v>1102.93399676485</v>
+      </c>
+      <c r="E19">
+        <v>-327.9429999999999</v>
+      </c>
+      <c r="F19">
+        <v>306.357</v>
+      </c>
+      <c r="G19">
+        <v>710.4</v>
+      </c>
+      <c r="H19">
+        <v>1167.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1184.4</v>
+      </c>
+      <c r="K19">
+        <v>189.2</v>
+      </c>
+      <c r="L19">
+        <v>995.2</v>
+      </c>
+      <c r="M19">
+        <v>14.0005149</v>
+      </c>
+      <c r="N19">
+        <v>981.1994851000001</v>
+      </c>
+      <c r="O19">
+        <v>235.487876424</v>
+      </c>
+      <c r="P19">
+        <v>745.7116086760001</v>
+      </c>
+      <c r="Q19">
+        <v>934.911608676</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1423563551047584</v>
+      </c>
+      <c r="T19">
+        <v>1.066745800147892</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>71.08309995084537</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1238044760845634</v>
+      </c>
+      <c r="C20">
+        <v>1489.533619566708</v>
+      </c>
+      <c r="D20">
+        <v>1103.511619566707</v>
+      </c>
+      <c r="E20">
+        <v>-309.922</v>
+      </c>
+      <c r="F20">
+        <v>324.378</v>
+      </c>
+      <c r="G20">
+        <v>710.4</v>
+      </c>
+      <c r="H20">
+        <v>1167.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1184.4</v>
+      </c>
+      <c r="K20">
+        <v>189.2</v>
+      </c>
+      <c r="L20">
+        <v>995.2</v>
+      </c>
+      <c r="M20">
+        <v>14.8240746</v>
+      </c>
+      <c r="N20">
+        <v>980.3759254</v>
+      </c>
+      <c r="O20">
+        <v>235.290222096</v>
+      </c>
+      <c r="P20">
+        <v>745.085703304</v>
+      </c>
+      <c r="Q20">
+        <v>934.285703304</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1433569708348334</v>
+      </c>
+      <c r="T20">
+        <v>1.077053256667964</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>67.13403884246507</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1235487374321774</v>
+      </c>
+      <c r="C21">
+        <v>1472.090847704751</v>
+      </c>
+      <c r="D21">
+        <v>1104.08984770475</v>
+      </c>
+      <c r="E21">
+        <v>-291.901</v>
+      </c>
+      <c r="F21">
+        <v>342.399</v>
+      </c>
+      <c r="G21">
+        <v>710.4</v>
+      </c>
+      <c r="H21">
+        <v>1167.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1184.4</v>
+      </c>
+      <c r="K21">
+        <v>189.2</v>
+      </c>
+      <c r="L21">
+        <v>995.2</v>
+      </c>
+      <c r="M21">
+        <v>15.6476343</v>
+      </c>
+      <c r="N21">
+        <v>979.5523657</v>
+      </c>
+      <c r="O21">
+        <v>235.092567768</v>
+      </c>
+      <c r="P21">
+        <v>744.459797932</v>
+      </c>
+      <c r="Q21">
+        <v>933.6597979319999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1443822931261449</v>
+      </c>
+      <c r="T21">
+        <v>1.087615218287298</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>63.60066837707218</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1232929987797913</v>
+      </c>
+      <c r="C22">
+        <v>1454.648682131046</v>
+      </c>
+      <c r="D22">
+        <v>1104.668682131046</v>
+      </c>
+      <c r="E22">
+        <v>-273.8799999999999</v>
+      </c>
+      <c r="F22">
+        <v>360.42</v>
+      </c>
+      <c r="G22">
+        <v>710.4</v>
+      </c>
+      <c r="H22">
+        <v>1167.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1184.4</v>
+      </c>
+      <c r="K22">
+        <v>189.2</v>
+      </c>
+      <c r="L22">
+        <v>995.2</v>
+      </c>
+      <c r="M22">
+        <v>16.471194</v>
+      </c>
+      <c r="N22">
+        <v>978.7288060000001</v>
+      </c>
+      <c r="O22">
+        <v>234.89491344</v>
+      </c>
+      <c r="P22">
+        <v>743.8338925600001</v>
+      </c>
+      <c r="Q22">
+        <v>933.0338925600001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1454332484747392</v>
+      </c>
+      <c r="T22">
+        <v>1.098441228947115</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>60.42063495821856</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1230372601274053</v>
+      </c>
+      <c r="C23">
+        <v>1437.207123799661</v>
+      </c>
+      <c r="D23">
+        <v>1105.248123799661</v>
+      </c>
+      <c r="E23">
+        <v>-255.859</v>
+      </c>
+      <c r="F23">
+        <v>378.441</v>
+      </c>
+      <c r="G23">
+        <v>710.4</v>
+      </c>
+      <c r="H23">
+        <v>1167.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1184.4</v>
+      </c>
+      <c r="K23">
+        <v>189.2</v>
+      </c>
+      <c r="L23">
+        <v>995.2</v>
+      </c>
+      <c r="M23">
+        <v>17.2947537</v>
+      </c>
+      <c r="N23">
+        <v>977.9052463</v>
+      </c>
+      <c r="O23">
+        <v>234.697259112</v>
+      </c>
+      <c r="P23">
+        <v>743.2079871880001</v>
+      </c>
+      <c r="Q23">
+        <v>932.4079871880001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1465108102878548</v>
+      </c>
+      <c r="T23">
+        <v>1.109541315826168</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>57.54346186497007</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1227815214750193</v>
+      </c>
+      <c r="C24">
+        <v>1419.766173666662</v>
+      </c>
+      <c r="D24">
+        <v>1105.828173666662</v>
+      </c>
+      <c r="E24">
+        <v>-237.838</v>
+      </c>
+      <c r="F24">
+        <v>396.462</v>
+      </c>
+      <c r="G24">
+        <v>710.4</v>
+      </c>
+      <c r="H24">
+        <v>1167.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1184.4</v>
+      </c>
+      <c r="K24">
+        <v>189.2</v>
+      </c>
+      <c r="L24">
+        <v>995.2</v>
+      </c>
+      <c r="M24">
+        <v>18.1183134</v>
+      </c>
+      <c r="N24">
+        <v>977.0816866</v>
+      </c>
+      <c r="O24">
+        <v>234.499604784</v>
+      </c>
+      <c r="P24">
+        <v>742.582081816</v>
+      </c>
+      <c r="Q24">
+        <v>931.7820818160001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1476160018910504</v>
+      </c>
+      <c r="T24">
+        <v>1.120926020317504</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>54.92784996201688</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1225257828226333</v>
+      </c>
+      <c r="C25">
+        <v>1402.325832690126</v>
+      </c>
+      <c r="D25">
+        <v>1106.408832690126</v>
+      </c>
+      <c r="E25">
+        <v>-219.817</v>
+      </c>
+      <c r="F25">
+        <v>414.483</v>
+      </c>
+      <c r="G25">
+        <v>710.4</v>
+      </c>
+      <c r="H25">
+        <v>1167.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1184.4</v>
+      </c>
+      <c r="K25">
+        <v>189.2</v>
+      </c>
+      <c r="L25">
+        <v>995.2</v>
+      </c>
+      <c r="M25">
+        <v>18.9418731</v>
+      </c>
+      <c r="N25">
+        <v>976.2581269000001</v>
+      </c>
+      <c r="O25">
+        <v>234.301950456</v>
+      </c>
+      <c r="P25">
+        <v>741.9561764440001</v>
+      </c>
+      <c r="Q25">
+        <v>931.156176444</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1487498997696536</v>
+      </c>
+      <c r="T25">
+        <v>1.132606431419005</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>52.53968257236397</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1222700441702472</v>
+      </c>
+      <c r="C26">
+        <v>1384.886101830142</v>
+      </c>
+      <c r="D26">
+        <v>1106.990101830142</v>
+      </c>
+      <c r="E26">
+        <v>-201.796</v>
+      </c>
+      <c r="F26">
+        <v>432.504</v>
+      </c>
+      <c r="G26">
+        <v>710.4</v>
+      </c>
+      <c r="H26">
+        <v>1167.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1184.4</v>
+      </c>
+      <c r="K26">
+        <v>189.2</v>
+      </c>
+      <c r="L26">
+        <v>995.2</v>
+      </c>
+      <c r="M26">
+        <v>19.7654328</v>
+      </c>
+      <c r="N26">
+        <v>975.4345672000001</v>
+      </c>
+      <c r="O26">
+        <v>234.104296128</v>
+      </c>
+      <c r="P26">
+        <v>741.3302710720001</v>
+      </c>
+      <c r="Q26">
+        <v>930.530271072</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1499136370661148</v>
+      </c>
+      <c r="T26">
+        <v>1.144594221760019</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>50.35052913184882</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1220143055178612</v>
+      </c>
+      <c r="C27">
+        <v>1367.446982048818</v>
+      </c>
+      <c r="D27">
+        <v>1107.571982048819</v>
+      </c>
+      <c r="E27">
+        <v>-183.775</v>
+      </c>
+      <c r="F27">
+        <v>450.525</v>
+      </c>
+      <c r="G27">
+        <v>710.4</v>
+      </c>
+      <c r="H27">
+        <v>1167.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1184.4</v>
+      </c>
+      <c r="K27">
+        <v>189.2</v>
+      </c>
+      <c r="L27">
+        <v>995.2</v>
+      </c>
+      <c r="M27">
+        <v>20.5889925</v>
+      </c>
+      <c r="N27">
+        <v>974.6110075</v>
+      </c>
+      <c r="O27">
+        <v>233.9066418</v>
+      </c>
+      <c r="P27">
+        <v>740.7043657</v>
+      </c>
+      <c r="Q27">
+        <v>929.9043657</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1511084073571483</v>
+      </c>
+      <c r="T27">
+        <v>1.156901686510126</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>48.33650796657486</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1217585668654752</v>
+      </c>
+      <c r="C28">
+        <v>1350.008474310288</v>
+      </c>
+      <c r="D28">
+        <v>1108.154474310288</v>
+      </c>
+      <c r="E28">
+        <v>-165.754</v>
+      </c>
+      <c r="F28">
+        <v>468.546</v>
+      </c>
+      <c r="G28">
+        <v>710.4</v>
+      </c>
+      <c r="H28">
+        <v>1167.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1184.4</v>
+      </c>
+      <c r="K28">
+        <v>189.2</v>
+      </c>
+      <c r="L28">
+        <v>995.2</v>
+      </c>
+      <c r="M28">
+        <v>21.4125522</v>
+      </c>
+      <c r="N28">
+        <v>973.7874478</v>
+      </c>
+      <c r="O28">
+        <v>233.708987472</v>
+      </c>
+      <c r="P28">
+        <v>740.078460328</v>
+      </c>
+      <c r="Q28">
+        <v>929.2784603279999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1523354687371286</v>
+      </c>
+      <c r="T28">
+        <v>1.16954178544267</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>46.47741150632198</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1215028282130892</v>
+      </c>
+      <c r="C29">
+        <v>1332.570579580711</v>
+      </c>
+      <c r="D29">
+        <v>1108.737579580711</v>
+      </c>
+      <c r="E29">
+        <v>-147.7329999999999</v>
+      </c>
+      <c r="F29">
+        <v>486.567</v>
+      </c>
+      <c r="G29">
+        <v>710.4</v>
+      </c>
+      <c r="H29">
+        <v>1167.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1184.4</v>
+      </c>
+      <c r="K29">
+        <v>189.2</v>
+      </c>
+      <c r="L29">
+        <v>995.2</v>
+      </c>
+      <c r="M29">
+        <v>22.2361119</v>
+      </c>
+      <c r="N29">
+        <v>972.9638881000001</v>
+      </c>
+      <c r="O29">
+        <v>233.511333144</v>
+      </c>
+      <c r="P29">
+        <v>739.4525549560001</v>
+      </c>
+      <c r="Q29">
+        <v>928.6525549560001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1535961482371084</v>
+      </c>
+      <c r="T29">
+        <v>1.182528188455556</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>44.75602589497672</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1212470895607031</v>
+      </c>
+      <c r="C30">
+        <v>1315.133298828285</v>
+      </c>
+      <c r="D30">
+        <v>1109.321298828285</v>
+      </c>
+      <c r="E30">
+        <v>-129.7119999999999</v>
+      </c>
+      <c r="F30">
+        <v>504.588</v>
+      </c>
+      <c r="G30">
+        <v>710.4</v>
+      </c>
+      <c r="H30">
+        <v>1167.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1184.4</v>
+      </c>
+      <c r="K30">
+        <v>189.2</v>
+      </c>
+      <c r="L30">
+        <v>995.2</v>
+      </c>
+      <c r="M30">
+        <v>23.05967160000001</v>
+      </c>
+      <c r="N30">
+        <v>972.1403284</v>
+      </c>
+      <c r="O30">
+        <v>233.313678816</v>
+      </c>
+      <c r="P30">
+        <v>738.8266495840001</v>
+      </c>
+      <c r="Q30">
+        <v>928.0266495840001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1548918466120877</v>
+      </c>
+      <c r="T30">
+        <v>1.195875324885468</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>43.15759639872754</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1209913509083171</v>
+      </c>
+      <c r="C31">
+        <v>1297.696633023244</v>
+      </c>
+      <c r="D31">
+        <v>1109.905633023244</v>
+      </c>
+      <c r="E31">
+        <v>-111.691</v>
+      </c>
+      <c r="F31">
+        <v>522.6089999999999</v>
+      </c>
+      <c r="G31">
+        <v>710.4</v>
+      </c>
+      <c r="H31">
+        <v>1167.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1184.4</v>
+      </c>
+      <c r="K31">
+        <v>189.2</v>
+      </c>
+      <c r="L31">
+        <v>995.2</v>
+      </c>
+      <c r="M31">
+        <v>23.8832313</v>
+      </c>
+      <c r="N31">
+        <v>971.3167687</v>
+      </c>
+      <c r="O31">
+        <v>233.116024488</v>
+      </c>
+      <c r="P31">
+        <v>738.200744212</v>
+      </c>
+      <c r="Q31">
+        <v>927.4007442120001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.156224043532841</v>
+      </c>
+      <c r="T31">
+        <v>1.209598436989461</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.24</v>
+      </c>
+      <c r="W31">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>41.66940341946109</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.120735612255931</v>
+      </c>
+      <c r="C32">
+        <v>1280.260583137872</v>
+      </c>
+      <c r="D32">
+        <v>1110.490583137872</v>
+      </c>
+      <c r="E32">
+        <v>-93.66999999999996</v>
+      </c>
+      <c r="F32">
+        <v>540.63</v>
+      </c>
+      <c r="G32">
+        <v>710.4</v>
+      </c>
+      <c r="H32">
+        <v>1167.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1184.4</v>
+      </c>
+      <c r="K32">
+        <v>189.2</v>
+      </c>
+      <c r="L32">
+        <v>995.2</v>
+      </c>
+      <c r="M32">
+        <v>24.706791</v>
+      </c>
+      <c r="N32">
+        <v>970.4932090000001</v>
+      </c>
+      <c r="O32">
+        <v>232.91837016</v>
+      </c>
+      <c r="P32">
+        <v>737.5748388400001</v>
+      </c>
+      <c r="Q32">
+        <v>926.77483884</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1575943032227586</v>
+      </c>
+      <c r="T32">
+        <v>1.223713638010711</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.24</v>
+      </c>
+      <c r="W32">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>40.28042330547905</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.120479873603545</v>
+      </c>
+      <c r="C33">
+        <v>1262.825150146499</v>
+      </c>
+      <c r="D33">
+        <v>1111.076150146499</v>
+      </c>
+      <c r="E33">
+        <v>-75.649</v>
+      </c>
+      <c r="F33">
+        <v>558.651</v>
+      </c>
+      <c r="G33">
+        <v>710.4</v>
+      </c>
+      <c r="H33">
+        <v>1167.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1184.4</v>
+      </c>
+      <c r="K33">
+        <v>189.2</v>
+      </c>
+      <c r="L33">
+        <v>995.2</v>
+      </c>
+      <c r="M33">
+        <v>25.5303507</v>
+      </c>
+      <c r="N33">
+        <v>969.6696493000001</v>
+      </c>
+      <c r="O33">
+        <v>232.720715832</v>
+      </c>
+      <c r="P33">
+        <v>736.9489334680001</v>
+      </c>
+      <c r="Q33">
+        <v>926.148933468</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1590042805848479</v>
+      </c>
+      <c r="T33">
+        <v>1.238237975293447</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.24</v>
+      </c>
+      <c r="W33">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>38.98105481175392</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.120224134951159</v>
+      </c>
+      <c r="C34">
+        <v>1245.390335025515</v>
+      </c>
+      <c r="D34">
+        <v>1111.662335025515</v>
+      </c>
+      <c r="E34">
+        <v>-57.62799999999993</v>
+      </c>
+      <c r="F34">
+        <v>576.672</v>
+      </c>
+      <c r="G34">
+        <v>710.4</v>
+      </c>
+      <c r="H34">
+        <v>1167.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1184.4</v>
+      </c>
+      <c r="K34">
+        <v>189.2</v>
+      </c>
+      <c r="L34">
+        <v>995.2</v>
+      </c>
+      <c r="M34">
+        <v>26.3539104</v>
+      </c>
+      <c r="N34">
+        <v>968.8460896</v>
+      </c>
+      <c r="O34">
+        <v>232.523061504</v>
+      </c>
+      <c r="P34">
+        <v>736.323028096</v>
+      </c>
+      <c r="Q34">
+        <v>925.523028096</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1604557278693515</v>
+      </c>
+      <c r="T34">
+        <v>1.253189498966852</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.24</v>
+      </c>
+      <c r="W34">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>37.76289684888661</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.119968396298773</v>
+      </c>
+      <c r="C35">
+        <v>1227.956138753368</v>
+      </c>
+      <c r="D35">
+        <v>1112.249138753368</v>
+      </c>
+      <c r="E35">
+        <v>-39.60699999999997</v>
+      </c>
+      <c r="F35">
+        <v>594.693</v>
+      </c>
+      <c r="G35">
+        <v>710.4</v>
+      </c>
+      <c r="H35">
+        <v>1167.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1184.4</v>
+      </c>
+      <c r="K35">
+        <v>189.2</v>
+      </c>
+      <c r="L35">
+        <v>995.2</v>
+      </c>
+      <c r="M35">
+        <v>27.1774701</v>
+      </c>
+      <c r="N35">
+        <v>968.0225299</v>
+      </c>
+      <c r="O35">
+        <v>232.325407176</v>
+      </c>
+      <c r="P35">
+        <v>735.697122724</v>
+      </c>
+      <c r="Q35">
+        <v>924.8971227239999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1619505019384671</v>
+      </c>
+      <c r="T35">
+        <v>1.268587336779761</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.24</v>
+      </c>
+      <c r="W35">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>36.61856664134459</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1197126576463869</v>
+      </c>
+      <c r="C36">
+        <v>1210.522562310577</v>
+      </c>
+      <c r="D36">
+        <v>1112.836562310577</v>
+      </c>
+      <c r="E36">
+        <v>-21.5859999999999</v>
+      </c>
+      <c r="F36">
+        <v>612.7140000000001</v>
+      </c>
+      <c r="G36">
+        <v>710.4</v>
+      </c>
+      <c r="H36">
+        <v>1167.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1184.4</v>
+      </c>
+      <c r="K36">
+        <v>189.2</v>
+      </c>
+      <c r="L36">
+        <v>995.2</v>
+      </c>
+      <c r="M36">
+        <v>28.0010298</v>
+      </c>
+      <c r="N36">
+        <v>967.1989702000001</v>
+      </c>
+      <c r="O36">
+        <v>232.127752848</v>
+      </c>
+      <c r="P36">
+        <v>735.0712173520001</v>
+      </c>
+      <c r="Q36">
+        <v>924.2712173520001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1634905721914954</v>
+      </c>
+      <c r="T36">
+        <v>1.284451775738516</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.24</v>
+      </c>
+      <c r="W36">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>35.54154997542268</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1194569189940009</v>
+      </c>
+      <c r="C37">
+        <v>1193.08960667973</v>
+      </c>
+      <c r="D37">
+        <v>1113.424606679731</v>
+      </c>
+      <c r="E37">
+        <v>-3.564999999999941</v>
+      </c>
+      <c r="F37">
+        <v>630.735</v>
+      </c>
+      <c r="G37">
+        <v>710.4</v>
+      </c>
+      <c r="H37">
+        <v>1167.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1184.4</v>
+      </c>
+      <c r="K37">
+        <v>189.2</v>
+      </c>
+      <c r="L37">
+        <v>995.2</v>
+      </c>
+      <c r="M37">
+        <v>28.8245895</v>
+      </c>
+      <c r="N37">
+        <v>966.3754105</v>
+      </c>
+      <c r="O37">
+        <v>231.93009852</v>
+      </c>
+      <c r="P37">
+        <v>734.44531198</v>
+      </c>
+      <c r="Q37">
+        <v>923.6453119800001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1650780292215399</v>
+      </c>
+      <c r="T37">
+        <v>1.300804351280617</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.24</v>
+      </c>
+      <c r="W37">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>34.52607711898204</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1192011803416149</v>
+      </c>
+      <c r="C38">
+        <v>1175.657272845496</v>
+      </c>
+      <c r="D38">
+        <v>1114.013272845496</v>
+      </c>
+      <c r="E38">
+        <v>14.45600000000002</v>
+      </c>
+      <c r="F38">
+        <v>648.756</v>
+      </c>
+      <c r="G38">
+        <v>710.4</v>
+      </c>
+      <c r="H38">
+        <v>1167.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1184.4</v>
+      </c>
+      <c r="K38">
+        <v>189.2</v>
+      </c>
+      <c r="L38">
+        <v>995.2</v>
+      </c>
+      <c r="M38">
+        <v>29.6481492</v>
+      </c>
+      <c r="N38">
+        <v>965.5518508</v>
+      </c>
+      <c r="O38">
+        <v>231.732444192</v>
+      </c>
+      <c r="P38">
+        <v>733.819406608</v>
+      </c>
+      <c r="Q38">
+        <v>923.0194066080001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1667150942837733</v>
+      </c>
+      <c r="T38">
+        <v>1.317667944808409</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.24</v>
+      </c>
+      <c r="W38">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>33.56701942123254</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1189454416892288</v>
+      </c>
+      <c r="C39">
+        <v>1158.225561794624</v>
+      </c>
+      <c r="D39">
+        <v>1114.602561794624</v>
+      </c>
+      <c r="E39">
+        <v>32.47699999999998</v>
+      </c>
+      <c r="F39">
+        <v>666.7769999999999</v>
+      </c>
+      <c r="G39">
+        <v>710.4</v>
+      </c>
+      <c r="H39">
+        <v>1167.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1184.4</v>
+      </c>
+      <c r="K39">
+        <v>189.2</v>
+      </c>
+      <c r="L39">
+        <v>995.2</v>
+      </c>
+      <c r="M39">
+        <v>30.4717089</v>
+      </c>
+      <c r="N39">
+        <v>964.7282911000001</v>
+      </c>
+      <c r="O39">
+        <v>231.534789864</v>
+      </c>
+      <c r="P39">
+        <v>733.1935012360001</v>
+      </c>
+      <c r="Q39">
+        <v>922.393501236</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1684041296654426</v>
+      </c>
+      <c r="T39">
+        <v>1.335066890511686</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.24</v>
+      </c>
+      <c r="W39">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>32.65980268011815</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1186897030368428</v>
+      </c>
+      <c r="C40">
+        <v>1140.794474515955</v>
+      </c>
+      <c r="D40">
+        <v>1115.192474515956</v>
+      </c>
+      <c r="E40">
+        <v>50.49800000000005</v>
+      </c>
+      <c r="F40">
+        <v>684.798</v>
+      </c>
+      <c r="G40">
+        <v>710.4</v>
+      </c>
+      <c r="H40">
+        <v>1167.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1184.4</v>
+      </c>
+      <c r="K40">
+        <v>189.2</v>
+      </c>
+      <c r="L40">
+        <v>995.2</v>
+      </c>
+      <c r="M40">
+        <v>31.2952686</v>
+      </c>
+      <c r="N40">
+        <v>963.9047314000001</v>
+      </c>
+      <c r="O40">
+        <v>231.337135536</v>
+      </c>
+      <c r="P40">
+        <v>732.5675958640001</v>
+      </c>
+      <c r="Q40">
+        <v>921.767595864</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1701476500594239</v>
+      </c>
+      <c r="T40">
+        <v>1.353027092527972</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.24</v>
+      </c>
+      <c r="W40">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>31.80033418853609</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1184339643844568</v>
+      </c>
+      <c r="C41">
+        <v>1123.364012000424</v>
+      </c>
+      <c r="D41">
+        <v>1115.783012000424</v>
+      </c>
+      <c r="E41">
+        <v>68.51900000000001</v>
+      </c>
+      <c r="F41">
+        <v>702.819</v>
+      </c>
+      <c r="G41">
+        <v>710.4</v>
+      </c>
+      <c r="H41">
+        <v>1167.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1184.4</v>
+      </c>
+      <c r="K41">
+        <v>189.2</v>
+      </c>
+      <c r="L41">
+        <v>995.2</v>
+      </c>
+      <c r="M41">
+        <v>32.1188283</v>
+      </c>
+      <c r="N41">
+        <v>963.0811717</v>
+      </c>
+      <c r="O41">
+        <v>231.139481208</v>
+      </c>
+      <c r="P41">
+        <v>731.941690492</v>
+      </c>
+      <c r="Q41">
+        <v>921.141690492</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1719483350564865</v>
+      </c>
+      <c r="T41">
+        <v>1.37157615362676</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.24</v>
+      </c>
+      <c r="W41">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>30.98494100421465</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1181782257320708</v>
+      </c>
+      <c r="C42">
+        <v>1105.934175241064</v>
+      </c>
+      <c r="D42">
+        <v>1116.374175241064</v>
+      </c>
+      <c r="E42">
+        <v>86.54000000000008</v>
+      </c>
+      <c r="F42">
+        <v>720.84</v>
+      </c>
+      <c r="G42">
+        <v>710.4</v>
+      </c>
+      <c r="H42">
+        <v>1167.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1184.4</v>
+      </c>
+      <c r="K42">
+        <v>189.2</v>
+      </c>
+      <c r="L42">
+        <v>995.2</v>
+      </c>
+      <c r="M42">
+        <v>32.94238800000001</v>
+      </c>
+      <c r="N42">
+        <v>962.257612</v>
+      </c>
+      <c r="O42">
+        <v>230.94182688</v>
+      </c>
+      <c r="P42">
+        <v>731.31578512</v>
+      </c>
+      <c r="Q42">
+        <v>920.5157851199999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1738090428867846</v>
+      </c>
+      <c r="T42">
+        <v>1.390743516762173</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.24</v>
+      </c>
+      <c r="W42">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>30.21031747910928</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1179224870796847</v>
+      </c>
+      <c r="C43">
+        <v>1088.504965233016</v>
+      </c>
+      <c r="D43">
+        <v>1116.965965233016</v>
+      </c>
+      <c r="E43">
+        <v>104.561</v>
+      </c>
+      <c r="F43">
+        <v>738.861</v>
+      </c>
+      <c r="G43">
+        <v>710.4</v>
+      </c>
+      <c r="H43">
+        <v>1167.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1184.4</v>
+      </c>
+      <c r="K43">
+        <v>189.2</v>
+      </c>
+      <c r="L43">
+        <v>995.2</v>
+      </c>
+      <c r="M43">
+        <v>33.76594770000001</v>
+      </c>
+      <c r="N43">
+        <v>961.4340523000001</v>
+      </c>
+      <c r="O43">
+        <v>230.744172552</v>
+      </c>
+      <c r="P43">
+        <v>730.6898797480001</v>
+      </c>
+      <c r="Q43">
+        <v>919.8898797480001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1757328255587877</v>
+      </c>
+      <c r="T43">
+        <v>1.410560621020821</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.24</v>
+      </c>
+      <c r="W43">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>29.47348046742369</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1176667484272987</v>
+      </c>
+      <c r="C44">
+        <v>1071.076382973531</v>
+      </c>
+      <c r="D44">
+        <v>1117.558382973531</v>
+      </c>
+      <c r="E44">
+        <v>122.582</v>
+      </c>
+      <c r="F44">
+        <v>756.8819999999999</v>
+      </c>
+      <c r="G44">
+        <v>710.4</v>
+      </c>
+      <c r="H44">
+        <v>1167.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1184.4</v>
+      </c>
+      <c r="K44">
+        <v>189.2</v>
+      </c>
+      <c r="L44">
+        <v>995.2</v>
+      </c>
+      <c r="M44">
+        <v>34.5895074</v>
+      </c>
+      <c r="N44">
+        <v>960.6104926</v>
+      </c>
+      <c r="O44">
+        <v>230.546518224</v>
+      </c>
+      <c r="P44">
+        <v>730.063974376</v>
+      </c>
+      <c r="Q44">
+        <v>919.2639743760001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1777229455643081</v>
+      </c>
+      <c r="T44">
+        <v>1.431061073702181</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.24</v>
+      </c>
+      <c r="W44">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>28.77173093248503</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1174110097749127</v>
+      </c>
+      <c r="C45">
+        <v>1053.648429461978</v>
+      </c>
+      <c r="D45">
+        <v>1118.151429461978</v>
+      </c>
+      <c r="E45">
+        <v>140.603</v>
+      </c>
+      <c r="F45">
+        <v>774.9029999999999</v>
+      </c>
+      <c r="G45">
+        <v>710.4</v>
+      </c>
+      <c r="H45">
+        <v>1167.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1184.4</v>
+      </c>
+      <c r="K45">
+        <v>189.2</v>
+      </c>
+      <c r="L45">
+        <v>995.2</v>
+      </c>
+      <c r="M45">
+        <v>35.4130671</v>
+      </c>
+      <c r="N45">
+        <v>959.7869329</v>
+      </c>
+      <c r="O45">
+        <v>230.348863896</v>
+      </c>
+      <c r="P45">
+        <v>729.438069004</v>
+      </c>
+      <c r="Q45">
+        <v>918.638069004</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1797828943419521</v>
+      </c>
+      <c r="T45">
+        <v>1.452280840512712</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.24</v>
+      </c>
+      <c r="W45">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>28.10262091079934</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1171552711225267</v>
+      </c>
+      <c r="C46">
+        <v>1036.221105699846</v>
+      </c>
+      <c r="D46">
+        <v>1118.745105699846</v>
+      </c>
+      <c r="E46">
+        <v>158.624</v>
+      </c>
+      <c r="F46">
+        <v>792.924</v>
+      </c>
+      <c r="G46">
+        <v>710.4</v>
+      </c>
+      <c r="H46">
+        <v>1167.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1184.4</v>
+      </c>
+      <c r="K46">
+        <v>189.2</v>
+      </c>
+      <c r="L46">
+        <v>995.2</v>
+      </c>
+      <c r="M46">
+        <v>36.2366268</v>
+      </c>
+      <c r="N46">
+        <v>958.9633732000001</v>
+      </c>
+      <c r="O46">
+        <v>230.151209568</v>
+      </c>
+      <c r="P46">
+        <v>728.8121636320001</v>
+      </c>
+      <c r="Q46">
+        <v>918.012163632</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1819164127187976</v>
+      </c>
+      <c r="T46">
+        <v>1.474258456137904</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.24</v>
+      </c>
+      <c r="W46">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>27.46392498100844</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1168995324701406</v>
+      </c>
+      <c r="C47">
+        <v>1018.794412690755</v>
+      </c>
+      <c r="D47">
+        <v>1119.339412690755</v>
+      </c>
+      <c r="E47">
+        <v>176.645</v>
+      </c>
+      <c r="F47">
+        <v>810.9449999999999</v>
+      </c>
+      <c r="G47">
+        <v>710.4</v>
+      </c>
+      <c r="H47">
+        <v>1167.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1184.4</v>
+      </c>
+      <c r="K47">
+        <v>189.2</v>
+      </c>
+      <c r="L47">
+        <v>995.2</v>
+      </c>
+      <c r="M47">
+        <v>37.0601865</v>
+      </c>
+      <c r="N47">
+        <v>958.1398135000001</v>
+      </c>
+      <c r="O47">
+        <v>229.95355524</v>
+      </c>
+      <c r="P47">
+        <v>728.18625826</v>
+      </c>
+      <c r="Q47">
+        <v>917.38625826</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1841275135820739</v>
+      </c>
+      <c r="T47">
+        <v>1.497035257785831</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0.24</v>
+      </c>
+      <c r="W47">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>26.85361553698603</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1166437938177546</v>
+      </c>
+      <c r="C48">
+        <v>1001.368351440457</v>
+      </c>
+      <c r="D48">
+        <v>1119.934351440457</v>
+      </c>
+      <c r="E48">
+        <v>194.6660000000001</v>
+      </c>
+      <c r="F48">
+        <v>828.966</v>
+      </c>
+      <c r="G48">
+        <v>710.4</v>
+      </c>
+      <c r="H48">
+        <v>1167.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1184.4</v>
+      </c>
+      <c r="K48">
+        <v>189.2</v>
+      </c>
+      <c r="L48">
+        <v>995.2</v>
+      </c>
+      <c r="M48">
+        <v>37.8837462</v>
+      </c>
+      <c r="N48">
+        <v>957.3162538</v>
+      </c>
+      <c r="O48">
+        <v>229.755900912</v>
+      </c>
+      <c r="P48">
+        <v>727.560352888</v>
+      </c>
+      <c r="Q48">
+        <v>916.7603528879999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1864205070699159</v>
+      </c>
+      <c r="T48">
+        <v>1.520655644679977</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0.24</v>
+      </c>
+      <c r="W48">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>26.26984128618199</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1163880551653686</v>
+      </c>
+      <c r="C49">
+        <v>983.9429229568433</v>
+      </c>
+      <c r="D49">
+        <v>1120.529922956843</v>
+      </c>
+      <c r="E49">
+        <v>212.687</v>
+      </c>
+      <c r="F49">
+        <v>846.987</v>
+      </c>
+      <c r="G49">
+        <v>710.4</v>
+      </c>
+      <c r="H49">
+        <v>1167.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1184.4</v>
+      </c>
+      <c r="K49">
+        <v>189.2</v>
+      </c>
+      <c r="L49">
+        <v>995.2</v>
+      </c>
+      <c r="M49">
+        <v>38.7073059</v>
+      </c>
+      <c r="N49">
+        <v>956.4926941</v>
+      </c>
+      <c r="O49">
+        <v>229.558246584</v>
+      </c>
+      <c r="P49">
+        <v>726.934447516</v>
+      </c>
+      <c r="Q49">
+        <v>916.1344475159999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1888000286139029</v>
+      </c>
+      <c r="T49">
+        <v>1.545167366928619</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0.24</v>
+      </c>
+      <c r="W49">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>25.71090849285897</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1161323165129825</v>
+      </c>
+      <c r="C50">
+        <v>966.5181282499515</v>
+      </c>
+      <c r="D50">
+        <v>1121.126128249952</v>
+      </c>
+      <c r="E50">
+        <v>230.708</v>
+      </c>
+      <c r="F50">
+        <v>865.0079999999999</v>
+      </c>
+      <c r="G50">
+        <v>710.4</v>
+      </c>
+      <c r="H50">
+        <v>1167.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1184.4</v>
+      </c>
+      <c r="K50">
+        <v>189.2</v>
+      </c>
+      <c r="L50">
+        <v>995.2</v>
+      </c>
+      <c r="M50">
+        <v>39.5308656</v>
+      </c>
+      <c r="N50">
+        <v>955.6691344000001</v>
+      </c>
+      <c r="O50">
+        <v>229.360592256</v>
+      </c>
+      <c r="P50">
+        <v>726.3085421440001</v>
+      </c>
+      <c r="Q50">
+        <v>915.5085421440001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1912710702172741</v>
+      </c>
+      <c r="T50">
+        <v>1.570621847725286</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0.24</v>
+      </c>
+      <c r="W50">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>25.17526456592441</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1158765778605965</v>
+      </c>
+      <c r="C51">
+        <v>949.093968331969</v>
+      </c>
+      <c r="D51">
+        <v>1121.722968331969</v>
+      </c>
+      <c r="E51">
+        <v>248.7289999999999</v>
+      </c>
+      <c r="F51">
+        <v>883.0289999999999</v>
+      </c>
+      <c r="G51">
+        <v>710.4</v>
+      </c>
+      <c r="H51">
+        <v>1167.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1184.4</v>
+      </c>
+      <c r="K51">
+        <v>189.2</v>
+      </c>
+      <c r="L51">
+        <v>995.2</v>
+      </c>
+      <c r="M51">
+        <v>40.3544253</v>
+      </c>
+      <c r="N51">
+        <v>954.8455747</v>
+      </c>
+      <c r="O51">
+        <v>229.162937928</v>
+      </c>
+      <c r="P51">
+        <v>725.682636772</v>
+      </c>
+      <c r="Q51">
+        <v>914.8826367720001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1938390154129343</v>
+      </c>
+      <c r="T51">
+        <v>1.597074543455156</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0.24</v>
+      </c>
+      <c r="W51">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>24.66148365641575</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1156208392082105</v>
+      </c>
+      <c r="C52">
+        <v>931.6704442172397</v>
+      </c>
+      <c r="D52">
+        <v>1122.32044421724</v>
+      </c>
+      <c r="E52">
+        <v>266.75</v>
+      </c>
+      <c r="F52">
+        <v>901.05</v>
+      </c>
+      <c r="G52">
+        <v>710.4</v>
+      </c>
+      <c r="H52">
+        <v>1167.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1184.4</v>
+      </c>
+      <c r="K52">
+        <v>189.2</v>
+      </c>
+      <c r="L52">
+        <v>995.2</v>
+      </c>
+      <c r="M52">
+        <v>41.177985</v>
+      </c>
+      <c r="N52">
+        <v>954.022015</v>
+      </c>
+      <c r="O52">
+        <v>228.9652836</v>
+      </c>
+      <c r="P52">
+        <v>725.0567314</v>
+      </c>
+      <c r="Q52">
+        <v>914.2567314</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.196509678416421</v>
+      </c>
+      <c r="T52">
+        <v>1.62458534701422</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0.24</v>
+      </c>
+      <c r="W52">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>24.16825398328743</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1153651005558245</v>
+      </c>
+      <c r="C53">
+        <v>914.2475569222705</v>
+      </c>
+      <c r="D53">
+        <v>1122.91855692227</v>
+      </c>
+      <c r="E53">
+        <v>284.7710000000001</v>
+      </c>
+      <c r="F53">
+        <v>919.071</v>
+      </c>
+      <c r="G53">
+        <v>710.4</v>
+      </c>
+      <c r="H53">
+        <v>1167.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1184.4</v>
+      </c>
+      <c r="K53">
+        <v>189.2</v>
+      </c>
+      <c r="L53">
+        <v>995.2</v>
+      </c>
+      <c r="M53">
+        <v>42.0015447</v>
+      </c>
+      <c r="N53">
+        <v>953.1984553000001</v>
+      </c>
+      <c r="O53">
+        <v>228.767629272</v>
+      </c>
+      <c r="P53">
+        <v>724.4308260280001</v>
+      </c>
+      <c r="Q53">
+        <v>913.630826028</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1992893480731111</v>
+      </c>
+      <c r="T53">
+        <v>1.653219040514471</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0.24</v>
+      </c>
+      <c r="W53">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>23.69436665028179</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1151093619034384</v>
+      </c>
+      <c r="C54">
+        <v>896.8253074657356</v>
+      </c>
+      <c r="D54">
+        <v>1123.517307465735</v>
+      </c>
+      <c r="E54">
+        <v>302.792</v>
+      </c>
+      <c r="F54">
+        <v>937.092</v>
+      </c>
+      <c r="G54">
+        <v>710.4</v>
+      </c>
+      <c r="H54">
+        <v>1167.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1184.4</v>
+      </c>
+      <c r="K54">
+        <v>189.2</v>
+      </c>
+      <c r="L54">
+        <v>995.2</v>
+      </c>
+      <c r="M54">
+        <v>42.8251044</v>
+      </c>
+      <c r="N54">
+        <v>952.3748956000001</v>
+      </c>
+      <c r="O54">
+        <v>228.569974944</v>
+      </c>
+      <c r="P54">
+        <v>723.804920656</v>
+      </c>
+      <c r="Q54">
+        <v>913.004920656</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2021848372988301</v>
+      </c>
+      <c r="T54">
+        <v>1.683045804577232</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0.24</v>
+      </c>
+      <c r="W54">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>23.23870575316099</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1148536232510524</v>
+      </c>
+      <c r="C55">
+        <v>879.4036968684834</v>
+      </c>
+      <c r="D55">
+        <v>1124.116696868483</v>
+      </c>
+      <c r="E55">
+        <v>320.8130000000001</v>
+      </c>
+      <c r="F55">
+        <v>955.1130000000001</v>
+      </c>
+      <c r="G55">
+        <v>710.4</v>
+      </c>
+      <c r="H55">
+        <v>1167.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1184.4</v>
+      </c>
+      <c r="K55">
+        <v>189.2</v>
+      </c>
+      <c r="L55">
+        <v>995.2</v>
+      </c>
+      <c r="M55">
+        <v>43.6486641</v>
+      </c>
+      <c r="N55">
+        <v>951.5513359</v>
+      </c>
+      <c r="O55">
+        <v>228.372320616</v>
+      </c>
+      <c r="P55">
+        <v>723.179015284</v>
+      </c>
+      <c r="Q55">
+        <v>912.3790152839999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2052035388320264</v>
+      </c>
+      <c r="T55">
+        <v>1.714141792642664</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0.24</v>
+      </c>
+      <c r="W55">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>22.80023960687493</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1145978845986664</v>
+      </c>
+      <c r="C56">
+        <v>861.9827261535424</v>
+      </c>
+      <c r="D56">
+        <v>1124.716726153542</v>
+      </c>
+      <c r="E56">
+        <v>338.8340000000001</v>
+      </c>
+      <c r="F56">
+        <v>973.134</v>
+      </c>
+      <c r="G56">
+        <v>710.4</v>
+      </c>
+      <c r="H56">
+        <v>1167.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1184.4</v>
+      </c>
+      <c r="K56">
+        <v>189.2</v>
+      </c>
+      <c r="L56">
+        <v>995.2</v>
+      </c>
+      <c r="M56">
+        <v>44.4722238</v>
+      </c>
+      <c r="N56">
+        <v>950.7277762</v>
+      </c>
+      <c r="O56">
+        <v>228.174666288</v>
+      </c>
+      <c r="P56">
+        <v>722.553109912</v>
+      </c>
+      <c r="Q56">
+        <v>911.7531099119999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2083534882579704</v>
+      </c>
+      <c r="T56">
+        <v>1.746589780189201</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0.24</v>
+      </c>
+      <c r="W56">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>22.37801294748836</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1143421459462803</v>
+      </c>
+      <c r="C57">
+        <v>844.562396346125</v>
+      </c>
+      <c r="D57">
+        <v>1125.317396346125</v>
+      </c>
+      <c r="E57">
+        <v>356.8550000000001</v>
+      </c>
+      <c r="F57">
+        <v>991.1550000000001</v>
+      </c>
+      <c r="G57">
+        <v>710.4</v>
+      </c>
+      <c r="H57">
+        <v>1167.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1184.4</v>
+      </c>
+      <c r="K57">
+        <v>189.2</v>
+      </c>
+      <c r="L57">
+        <v>995.2</v>
+      </c>
+      <c r="M57">
+        <v>45.29578350000001</v>
+      </c>
+      <c r="N57">
+        <v>949.9042165000001</v>
+      </c>
+      <c r="O57">
+        <v>227.97701196</v>
+      </c>
+      <c r="P57">
+        <v>721.92720454</v>
+      </c>
+      <c r="Q57">
+        <v>911.1272045400001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2116434354361786</v>
+      </c>
+      <c r="T57">
+        <v>1.780479900515585</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0.24</v>
+      </c>
+      <c r="W57">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>21.97113998480675</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1140864072938943</v>
+      </c>
+      <c r="C58">
+        <v>827.1427084736373</v>
+      </c>
+      <c r="D58">
+        <v>1125.918708473637</v>
+      </c>
+      <c r="E58">
+        <v>374.8760000000001</v>
+      </c>
+      <c r="F58">
+        <v>1009.176</v>
+      </c>
+      <c r="G58">
+        <v>710.4</v>
+      </c>
+      <c r="H58">
+        <v>1167.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1184.4</v>
+      </c>
+      <c r="K58">
+        <v>189.2</v>
+      </c>
+      <c r="L58">
+        <v>995.2</v>
+      </c>
+      <c r="M58">
+        <v>46.11934320000001</v>
+      </c>
+      <c r="N58">
+        <v>949.0806568</v>
+      </c>
+      <c r="O58">
+        <v>227.779357632</v>
+      </c>
+      <c r="P58">
+        <v>721.301299168</v>
+      </c>
+      <c r="Q58">
+        <v>910.5012991680001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2150829256679416</v>
+      </c>
+      <c r="T58">
+        <v>1.815910480856804</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0.24</v>
+      </c>
+      <c r="W58">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>21.57879819936377</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1138306686415083</v>
+      </c>
+      <c r="C59">
+        <v>809.72366356568</v>
+      </c>
+      <c r="D59">
+        <v>1126.52066356568</v>
+      </c>
+      <c r="E59">
+        <v>392.8970000000002</v>
+      </c>
+      <c r="F59">
+        <v>1027.197</v>
+      </c>
+      <c r="G59">
+        <v>710.4</v>
+      </c>
+      <c r="H59">
+        <v>1167.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1184.4</v>
+      </c>
+      <c r="K59">
+        <v>189.2</v>
+      </c>
+      <c r="L59">
+        <v>995.2</v>
+      </c>
+      <c r="M59">
+        <v>46.94290290000001</v>
+      </c>
+      <c r="N59">
+        <v>948.2570971</v>
+      </c>
+      <c r="O59">
+        <v>227.581703304</v>
+      </c>
+      <c r="P59">
+        <v>720.675393796</v>
+      </c>
+      <c r="Q59">
+        <v>909.875393796</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2186823921895542</v>
+      </c>
+      <c r="T59">
+        <v>1.852988995167382</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0.24</v>
+      </c>
+      <c r="W59">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>21.20022279235739</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1135749299891223</v>
+      </c>
+      <c r="C60">
+        <v>792.3052626540589</v>
+      </c>
+      <c r="D60">
+        <v>1127.123262654059</v>
+      </c>
+      <c r="E60">
+        <v>410.9179999999999</v>
+      </c>
+      <c r="F60">
+        <v>1045.218</v>
+      </c>
+      <c r="G60">
+        <v>710.4</v>
+      </c>
+      <c r="H60">
+        <v>1167.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1184.4</v>
+      </c>
+      <c r="K60">
+        <v>189.2</v>
+      </c>
+      <c r="L60">
+        <v>995.2</v>
+      </c>
+      <c r="M60">
+        <v>47.7664626</v>
+      </c>
+      <c r="N60">
+        <v>947.4335374000001</v>
+      </c>
+      <c r="O60">
+        <v>227.384048976</v>
+      </c>
+      <c r="P60">
+        <v>720.0494884240001</v>
+      </c>
+      <c r="Q60">
+        <v>909.249488424</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2224532618788625</v>
+      </c>
+      <c r="T60">
+        <v>1.891833153016559</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0.24</v>
+      </c>
+      <c r="W60">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>20.83470170973055</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1133191913367362</v>
+      </c>
+      <c r="C61">
+        <v>774.8875067727865</v>
+      </c>
+      <c r="D61">
+        <v>1127.726506772786</v>
+      </c>
+      <c r="E61">
+        <v>428.9389999999999</v>
+      </c>
+      <c r="F61">
+        <v>1063.239</v>
+      </c>
+      <c r="G61">
+        <v>710.4</v>
+      </c>
+      <c r="H61">
+        <v>1167.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1184.4</v>
+      </c>
+      <c r="K61">
+        <v>189.2</v>
+      </c>
+      <c r="L61">
+        <v>995.2</v>
+      </c>
+      <c r="M61">
+        <v>48.59002229999999</v>
+      </c>
+      <c r="N61">
+        <v>946.6099777000001</v>
+      </c>
+      <c r="O61">
+        <v>227.186394648</v>
+      </c>
+      <c r="P61">
+        <v>719.423583052</v>
+      </c>
+      <c r="Q61">
+        <v>908.623583052</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.226408076431064</v>
+      </c>
+      <c r="T61">
+        <v>1.932572147833989</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0.24</v>
+      </c>
+      <c r="W61">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>20.48157117227749</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1130634526843502</v>
+      </c>
+      <c r="C62">
+        <v>757.4703969580926</v>
+      </c>
+      <c r="D62">
+        <v>1128.330396958093</v>
+      </c>
+      <c r="E62">
+        <v>446.96</v>
+      </c>
+      <c r="F62">
+        <v>1081.26</v>
+      </c>
+      <c r="G62">
+        <v>710.4</v>
+      </c>
+      <c r="H62">
+        <v>1167.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1184.4</v>
+      </c>
+      <c r="K62">
+        <v>189.2</v>
+      </c>
+      <c r="L62">
+        <v>995.2</v>
+      </c>
+      <c r="M62">
+        <v>49.41358200000001</v>
+      </c>
+      <c r="N62">
+        <v>945.786418</v>
+      </c>
+      <c r="O62">
+        <v>226.98874032</v>
+      </c>
+      <c r="P62">
+        <v>718.79767768</v>
+      </c>
+      <c r="Q62">
+        <v>907.9976776799999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2305606317108755</v>
+      </c>
+      <c r="T62">
+        <v>1.97534809239229</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0.24</v>
+      </c>
+      <c r="W62">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>20.14021165273952</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1128077140319642</v>
+      </c>
+      <c r="C63">
+        <v>740.0539342484262</v>
+      </c>
+      <c r="D63">
+        <v>1128.934934248426</v>
+      </c>
+      <c r="E63">
+        <v>464.981</v>
+      </c>
+      <c r="F63">
+        <v>1099.281</v>
+      </c>
+      <c r="G63">
+        <v>710.4</v>
+      </c>
+      <c r="H63">
+        <v>1167.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1184.4</v>
+      </c>
+      <c r="K63">
+        <v>189.2</v>
+      </c>
+      <c r="L63">
+        <v>995.2</v>
+      </c>
+      <c r="M63">
+        <v>50.2371417</v>
+      </c>
+      <c r="N63">
+        <v>944.9628583</v>
+      </c>
+      <c r="O63">
+        <v>226.791085992</v>
+      </c>
+      <c r="P63">
+        <v>718.1717723080001</v>
+      </c>
+      <c r="Q63">
+        <v>907.3717723080001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2349261385434978</v>
+      </c>
+      <c r="T63">
+        <v>2.020317675133068</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0.24</v>
+      </c>
+      <c r="W63">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>19.81004424859625</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1125519753795782</v>
+      </c>
+      <c r="C64">
+        <v>722.6381196844634</v>
+      </c>
+      <c r="D64">
+        <v>1129.540119684463</v>
+      </c>
+      <c r="E64">
+        <v>483.002</v>
+      </c>
+      <c r="F64">
+        <v>1117.302</v>
+      </c>
+      <c r="G64">
+        <v>710.4</v>
+      </c>
+      <c r="H64">
+        <v>1167.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1184.4</v>
+      </c>
+      <c r="K64">
+        <v>189.2</v>
+      </c>
+      <c r="L64">
+        <v>995.2</v>
+      </c>
+      <c r="M64">
+        <v>51.0607014</v>
+      </c>
+      <c r="N64">
+        <v>944.1392986000001</v>
+      </c>
+      <c r="O64">
+        <v>226.593431664</v>
+      </c>
+      <c r="P64">
+        <v>717.545866936</v>
+      </c>
+      <c r="Q64">
+        <v>906.7458669360001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2395214088936267</v>
+      </c>
+      <c r="T64">
+        <v>2.067654078018099</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0.24</v>
+      </c>
+      <c r="W64">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>19.49052740587696</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1122962367271921</v>
+      </c>
+      <c r="C65">
+        <v>705.2229543091134</v>
+      </c>
+      <c r="D65">
+        <v>1130.145954309113</v>
+      </c>
+      <c r="E65">
+        <v>501.0229999999999</v>
+      </c>
+      <c r="F65">
+        <v>1135.323</v>
+      </c>
+      <c r="G65">
+        <v>710.4</v>
+      </c>
+      <c r="H65">
+        <v>1167.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1184.4</v>
+      </c>
+      <c r="K65">
+        <v>189.2</v>
+      </c>
+      <c r="L65">
+        <v>995.2</v>
+      </c>
+      <c r="M65">
+        <v>51.8842611</v>
+      </c>
+      <c r="N65">
+        <v>943.3157389</v>
+      </c>
+      <c r="O65">
+        <v>226.395777336</v>
+      </c>
+      <c r="P65">
+        <v>716.919961564</v>
+      </c>
+      <c r="Q65">
+        <v>906.1199615640001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2443650722356543</v>
+      </c>
+      <c r="T65">
+        <v>2.1175492053834</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0.24</v>
+      </c>
+      <c r="W65">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>19.18115395499003</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1120404980748061</v>
+      </c>
+      <c r="C66">
+        <v>687.8084391675229</v>
+      </c>
+      <c r="D66">
+        <v>1130.752439167523</v>
+      </c>
+      <c r="E66">
+        <v>519.0440000000001</v>
+      </c>
+      <c r="F66">
+        <v>1153.344</v>
+      </c>
+      <c r="G66">
+        <v>710.4</v>
+      </c>
+      <c r="H66">
+        <v>1167.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1184.4</v>
+      </c>
+      <c r="K66">
+        <v>189.2</v>
+      </c>
+      <c r="L66">
+        <v>995.2</v>
+      </c>
+      <c r="M66">
+        <v>52.70782080000001</v>
+      </c>
+      <c r="N66">
+        <v>942.4921792</v>
+      </c>
+      <c r="O66">
+        <v>226.198123008</v>
+      </c>
+      <c r="P66">
+        <v>716.294056192</v>
+      </c>
+      <c r="Q66">
+        <v>905.494056192</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2494778279855724</v>
+      </c>
+      <c r="T66">
+        <v>2.170216284268996</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0.24</v>
+      </c>
+      <c r="W66">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>18.8814484244433</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1117847594224201</v>
+      </c>
+      <c r="C67">
+        <v>670.3945753070846</v>
+      </c>
+      <c r="D67">
+        <v>1131.359575307084</v>
+      </c>
+      <c r="E67">
+        <v>537.0650000000001</v>
+      </c>
+      <c r="F67">
+        <v>1171.365</v>
+      </c>
+      <c r="G67">
+        <v>710.4</v>
+      </c>
+      <c r="H67">
+        <v>1167.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1184.4</v>
+      </c>
+      <c r="K67">
+        <v>189.2</v>
+      </c>
+      <c r="L67">
+        <v>995.2</v>
+      </c>
+      <c r="M67">
+        <v>53.5313805</v>
+      </c>
+      <c r="N67">
+        <v>941.6686195000001</v>
+      </c>
+      <c r="O67">
+        <v>226.00046868</v>
+      </c>
+      <c r="P67">
+        <v>715.6681508200001</v>
+      </c>
+      <c r="Q67">
+        <v>904.86815082</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2548827412069145</v>
+      </c>
+      <c r="T67">
+        <v>2.225892910519484</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0.24</v>
+      </c>
+      <c r="W67">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>18.59096460252879</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.111529020770034</v>
+      </c>
+      <c r="C68">
+        <v>652.9813637774409</v>
+      </c>
+      <c r="D68">
+        <v>1131.967363777441</v>
+      </c>
+      <c r="E68">
+        <v>555.086</v>
+      </c>
+      <c r="F68">
+        <v>1189.386</v>
+      </c>
+      <c r="G68">
+        <v>710.4</v>
+      </c>
+      <c r="H68">
+        <v>1167.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1184.4</v>
+      </c>
+      <c r="K68">
+        <v>189.2</v>
+      </c>
+      <c r="L68">
+        <v>995.2</v>
+      </c>
+      <c r="M68">
+        <v>54.3549402</v>
+      </c>
+      <c r="N68">
+        <v>940.8450598000001</v>
+      </c>
+      <c r="O68">
+        <v>225.802814352</v>
+      </c>
+      <c r="P68">
+        <v>715.042245448</v>
+      </c>
+      <c r="Q68">
+        <v>904.2422454479999</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2606055905001001</v>
+      </c>
+      <c r="T68">
+        <v>2.284844632431764</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0.24</v>
+      </c>
+      <c r="W68">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>18.3092833206723</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.111273282117648</v>
+      </c>
+      <c r="C69">
+        <v>635.5688056304919</v>
+      </c>
+      <c r="D69">
+        <v>1132.575805630492</v>
+      </c>
+      <c r="E69">
+        <v>573.107</v>
+      </c>
+      <c r="F69">
+        <v>1207.407</v>
+      </c>
+      <c r="G69">
+        <v>710.4</v>
+      </c>
+      <c r="H69">
+        <v>1167.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1184.4</v>
+      </c>
+      <c r="K69">
+        <v>189.2</v>
+      </c>
+      <c r="L69">
+        <v>995.2</v>
+      </c>
+      <c r="M69">
+        <v>55.1784999</v>
+      </c>
+      <c r="N69">
+        <v>940.0215001</v>
+      </c>
+      <c r="O69">
+        <v>225.605160024</v>
+      </c>
+      <c r="P69">
+        <v>714.4163400760001</v>
+      </c>
+      <c r="Q69">
+        <v>903.6163400760001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2666752791443879</v>
+      </c>
+      <c r="T69">
+        <v>2.347369185975093</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0.24</v>
+      </c>
+      <c r="W69">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>18.03601043528913</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.111017543465262</v>
+      </c>
+      <c r="C70">
+        <v>618.1569019204001</v>
+      </c>
+      <c r="D70">
+        <v>1133.1849019204</v>
+      </c>
+      <c r="E70">
+        <v>591.1280000000002</v>
+      </c>
+      <c r="F70">
+        <v>1225.428</v>
+      </c>
+      <c r="G70">
+        <v>710.4</v>
+      </c>
+      <c r="H70">
+        <v>1167.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1184.4</v>
+      </c>
+      <c r="K70">
+        <v>189.2</v>
+      </c>
+      <c r="L70">
+        <v>995.2</v>
+      </c>
+      <c r="M70">
+        <v>56.00205960000001</v>
+      </c>
+      <c r="N70">
+        <v>939.1979404</v>
+      </c>
+      <c r="O70">
+        <v>225.407505696</v>
+      </c>
+      <c r="P70">
+        <v>713.7904347040001</v>
+      </c>
+      <c r="Q70">
+        <v>902.9904347040001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2731243233289437</v>
+      </c>
+      <c r="T70">
+        <v>2.413801524114878</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0.24</v>
+      </c>
+      <c r="W70">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>17.77077498771134</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.110761804812876</v>
+      </c>
+      <c r="C71">
+        <v>600.7456537035969</v>
+      </c>
+      <c r="D71">
+        <v>1133.794653703597</v>
+      </c>
+      <c r="E71">
+        <v>609.1490000000001</v>
+      </c>
+      <c r="F71">
+        <v>1243.449</v>
+      </c>
+      <c r="G71">
+        <v>710.4</v>
+      </c>
+      <c r="H71">
+        <v>1167.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1184.4</v>
+      </c>
+      <c r="K71">
+        <v>189.2</v>
+      </c>
+      <c r="L71">
+        <v>995.2</v>
+      </c>
+      <c r="M71">
+        <v>56.82561930000001</v>
+      </c>
+      <c r="N71">
+        <v>938.3743807000001</v>
+      </c>
+      <c r="O71">
+        <v>225.209851368</v>
+      </c>
+      <c r="P71">
+        <v>713.164529332</v>
+      </c>
+      <c r="Q71">
+        <v>902.3645293320001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2799894348802451</v>
+      </c>
+      <c r="T71">
+        <v>2.484519819554006</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0.24</v>
+      </c>
+      <c r="W71">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>17.51322752412133</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1105060661604899</v>
+      </c>
+      <c r="C72">
+        <v>583.3350620387885</v>
+      </c>
+      <c r="D72">
+        <v>1134.405062038789</v>
+      </c>
+      <c r="E72">
+        <v>627.1700000000001</v>
+      </c>
+      <c r="F72">
+        <v>1261.47</v>
+      </c>
+      <c r="G72">
+        <v>710.4</v>
+      </c>
+      <c r="H72">
+        <v>1167.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1184.4</v>
+      </c>
+      <c r="K72">
+        <v>189.2</v>
+      </c>
+      <c r="L72">
+        <v>995.2</v>
+      </c>
+      <c r="M72">
+        <v>57.649179</v>
+      </c>
+      <c r="N72">
+        <v>937.550821</v>
+      </c>
+      <c r="O72">
+        <v>225.01219704</v>
+      </c>
+      <c r="P72">
+        <v>712.53862396</v>
+      </c>
+      <c r="Q72">
+        <v>901.73862396</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2873122205349664</v>
+      </c>
+      <c r="T72">
+        <v>2.559952668022408</v>
+      </c>
+      <c r="U72">
+        <v>0.0457</v>
+      </c>
+      <c r="V72">
+        <v>0.24</v>
+      </c>
+      <c r="W72">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>17.26303855949102</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1102503275081039</v>
+      </c>
+      <c r="C73">
+        <v>565.9251279869629</v>
+      </c>
+      <c r="D73">
+        <v>1135.016127986963</v>
+      </c>
+      <c r="E73">
+        <v>645.1909999999998</v>
+      </c>
+      <c r="F73">
+        <v>1279.491</v>
+      </c>
+      <c r="G73">
+        <v>710.4</v>
+      </c>
+      <c r="H73">
+        <v>1167.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1184.4</v>
+      </c>
+      <c r="K73">
+        <v>189.2</v>
+      </c>
+      <c r="L73">
+        <v>995.2</v>
+      </c>
+      <c r="M73">
+        <v>58.47273869999999</v>
+      </c>
+      <c r="N73">
+        <v>936.7272613</v>
+      </c>
+      <c r="O73">
+        <v>224.814542712</v>
+      </c>
+      <c r="P73">
+        <v>711.912718588</v>
+      </c>
+      <c r="Q73">
+        <v>901.112718588</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2951400258900134</v>
+      </c>
+      <c r="T73">
+        <v>2.640587781902424</v>
+      </c>
+      <c r="U73">
+        <v>0.0457</v>
+      </c>
+      <c r="V73">
+        <v>0.24</v>
+      </c>
+      <c r="W73">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>17.01989717132918</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1099945888557179</v>
+      </c>
+      <c r="C74">
+        <v>548.5158526113944</v>
+      </c>
+      <c r="D74">
+        <v>1135.627852611394</v>
+      </c>
+      <c r="E74">
+        <v>663.212</v>
+      </c>
+      <c r="F74">
+        <v>1297.512</v>
+      </c>
+      <c r="G74">
+        <v>710.4</v>
+      </c>
+      <c r="H74">
+        <v>1167.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1184.4</v>
+      </c>
+      <c r="K74">
+        <v>189.2</v>
+      </c>
+      <c r="L74">
+        <v>995.2</v>
+      </c>
+      <c r="M74">
+        <v>59.2962984</v>
+      </c>
+      <c r="N74">
+        <v>935.9037016000001</v>
+      </c>
+      <c r="O74">
+        <v>224.616888384</v>
+      </c>
+      <c r="P74">
+        <v>711.286813216</v>
+      </c>
+      <c r="Q74">
+        <v>900.486813216</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3035269601989923</v>
+      </c>
+      <c r="T74">
+        <v>2.726982546773869</v>
+      </c>
+      <c r="U74">
+        <v>0.0457</v>
+      </c>
+      <c r="V74">
+        <v>0.24</v>
+      </c>
+      <c r="W74">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>16.78350971061627</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1097388502033318</v>
+      </c>
+      <c r="C75">
+        <v>531.1072369776516</v>
+      </c>
+      <c r="D75">
+        <v>1136.240236977652</v>
+      </c>
+      <c r="E75">
+        <v>681.2329999999999</v>
+      </c>
+      <c r="F75">
+        <v>1315.533</v>
+      </c>
+      <c r="G75">
+        <v>710.4</v>
+      </c>
+      <c r="H75">
+        <v>1167.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1184.4</v>
+      </c>
+      <c r="K75">
+        <v>189.2</v>
+      </c>
+      <c r="L75">
+        <v>995.2</v>
+      </c>
+      <c r="M75">
+        <v>60.1198581</v>
+      </c>
+      <c r="N75">
+        <v>935.0801419000001</v>
+      </c>
+      <c r="O75">
+        <v>224.419234056</v>
+      </c>
+      <c r="P75">
+        <v>710.6609078440001</v>
+      </c>
+      <c r="Q75">
+        <v>899.8609078440002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.312535148901229</v>
+      </c>
+      <c r="T75">
+        <v>2.819776923858015</v>
+      </c>
+      <c r="U75">
+        <v>0.0457</v>
+      </c>
+      <c r="V75">
+        <v>0.24</v>
+      </c>
+      <c r="W75">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>16.55359861869002</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1094831115509458</v>
+      </c>
+      <c r="C76">
+        <v>513.699282153603</v>
+      </c>
+      <c r="D76">
+        <v>1136.853282153603</v>
+      </c>
+      <c r="E76">
+        <v>699.2539999999999</v>
+      </c>
+      <c r="F76">
+        <v>1333.554</v>
+      </c>
+      <c r="G76">
+        <v>710.4</v>
+      </c>
+      <c r="H76">
+        <v>1167.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1184.4</v>
+      </c>
+      <c r="K76">
+        <v>189.2</v>
+      </c>
+      <c r="L76">
+        <v>995.2</v>
+      </c>
+      <c r="M76">
+        <v>60.9434178</v>
+      </c>
+      <c r="N76">
+        <v>934.2565822</v>
+      </c>
+      <c r="O76">
+        <v>224.221579728</v>
+      </c>
+      <c r="P76">
+        <v>710.0350024720001</v>
+      </c>
+      <c r="Q76">
+        <v>899.2350024720001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3222362751959453</v>
+      </c>
+      <c r="T76">
+        <v>2.919709329948633</v>
+      </c>
+      <c r="U76">
+        <v>0.0457</v>
+      </c>
+      <c r="V76">
+        <v>0.24</v>
+      </c>
+      <c r="W76">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>16.32990134005907</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1092273728985598</v>
+      </c>
+      <c r="C77">
+        <v>496.2919892094219</v>
+      </c>
+      <c r="D77">
+        <v>1137.466989209422</v>
+      </c>
+      <c r="E77">
+        <v>717.2749999999999</v>
+      </c>
+      <c r="F77">
+        <v>1351.575</v>
+      </c>
+      <c r="G77">
+        <v>710.4</v>
+      </c>
+      <c r="H77">
+        <v>1167.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1184.4</v>
+      </c>
+      <c r="K77">
+        <v>189.2</v>
+      </c>
+      <c r="L77">
+        <v>995.2</v>
+      </c>
+      <c r="M77">
+        <v>61.7669775</v>
+      </c>
+      <c r="N77">
+        <v>933.4330225000001</v>
+      </c>
+      <c r="O77">
+        <v>224.0239254</v>
+      </c>
+      <c r="P77">
+        <v>709.4090971000001</v>
+      </c>
+      <c r="Q77">
+        <v>898.6090971000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3327134915942391</v>
+      </c>
+      <c r="T77">
+        <v>3.027636328526501</v>
+      </c>
+      <c r="U77">
+        <v>0.0457</v>
+      </c>
+      <c r="V77">
+        <v>0.24</v>
+      </c>
+      <c r="W77">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>16.11216932219162</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1089716342461737</v>
+      </c>
+      <c r="C78">
+        <v>478.8853592175947</v>
+      </c>
+      <c r="D78">
+        <v>1138.081359217595</v>
+      </c>
+      <c r="E78">
+        <v>735.296</v>
+      </c>
+      <c r="F78">
+        <v>1369.596</v>
+      </c>
+      <c r="G78">
+        <v>710.4</v>
+      </c>
+      <c r="H78">
+        <v>1167.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1184.4</v>
+      </c>
+      <c r="K78">
+        <v>189.2</v>
+      </c>
+      <c r="L78">
+        <v>995.2</v>
+      </c>
+      <c r="M78">
+        <v>62.59053720000001</v>
+      </c>
+      <c r="N78">
+        <v>932.6094628000001</v>
+      </c>
+      <c r="O78">
+        <v>223.826271072</v>
+      </c>
+      <c r="P78">
+        <v>708.783191728</v>
+      </c>
+      <c r="Q78">
+        <v>897.9831917280001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3440638093590572</v>
+      </c>
+      <c r="T78">
+        <v>3.144557243652525</v>
+      </c>
+      <c r="U78">
+        <v>0.0457</v>
+      </c>
+      <c r="V78">
+        <v>0.24</v>
+      </c>
+      <c r="W78">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>15.90016709426805</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1087158955937877</v>
+      </c>
+      <c r="C79">
+        <v>461.4793932529253</v>
+      </c>
+      <c r="D79">
+        <v>1138.696393252925</v>
+      </c>
+      <c r="E79">
+        <v>753.317</v>
+      </c>
+      <c r="F79">
+        <v>1387.617</v>
+      </c>
+      <c r="G79">
+        <v>710.4</v>
+      </c>
+      <c r="H79">
+        <v>1167.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1184.4</v>
+      </c>
+      <c r="K79">
+        <v>189.2</v>
+      </c>
+      <c r="L79">
+        <v>995.2</v>
+      </c>
+      <c r="M79">
+        <v>63.4140969</v>
+      </c>
+      <c r="N79">
+        <v>931.7859031</v>
+      </c>
+      <c r="O79">
+        <v>223.628616744</v>
+      </c>
+      <c r="P79">
+        <v>708.157286356</v>
+      </c>
+      <c r="Q79">
+        <v>897.357286356</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3564011112773379</v>
+      </c>
+      <c r="T79">
+        <v>3.271645194876463</v>
+      </c>
+      <c r="U79">
+        <v>0.0457</v>
+      </c>
+      <c r="V79">
+        <v>0.24</v>
+      </c>
+      <c r="W79">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>15.69367141771911</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1084601569414017</v>
+      </c>
+      <c r="C80">
+        <v>444.0740923925432</v>
+      </c>
+      <c r="D80">
+        <v>1139.312092392543</v>
+      </c>
+      <c r="E80">
+        <v>771.338</v>
+      </c>
+      <c r="F80">
+        <v>1405.638</v>
+      </c>
+      <c r="G80">
+        <v>710.4</v>
+      </c>
+      <c r="H80">
+        <v>1167.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1184.4</v>
+      </c>
+      <c r="K80">
+        <v>189.2</v>
+      </c>
+      <c r="L80">
+        <v>995.2</v>
+      </c>
+      <c r="M80">
+        <v>64.23765660000001</v>
+      </c>
+      <c r="N80">
+        <v>930.9623434</v>
+      </c>
+      <c r="O80">
+        <v>223.430962416</v>
+      </c>
+      <c r="P80">
+        <v>707.531380984</v>
+      </c>
+      <c r="Q80">
+        <v>896.731380984</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3698599860972804</v>
+      </c>
+      <c r="T80">
+        <v>3.410286596211669</v>
+      </c>
+      <c r="U80">
+        <v>0.0457</v>
+      </c>
+      <c r="V80">
+        <v>0.24</v>
+      </c>
+      <c r="W80">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>15.49247050210732</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1082044182890157</v>
+      </c>
+      <c r="C81">
+        <v>426.6694577159078</v>
+      </c>
+      <c r="D81">
+        <v>1139.928457715908</v>
+      </c>
+      <c r="E81">
+        <v>789.3590000000002</v>
+      </c>
+      <c r="F81">
+        <v>1423.659</v>
+      </c>
+      <c r="G81">
+        <v>710.4</v>
+      </c>
+      <c r="H81">
+        <v>1167.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1184.4</v>
+      </c>
+      <c r="K81">
+        <v>189.2</v>
+      </c>
+      <c r="L81">
+        <v>995.2</v>
+      </c>
+      <c r="M81">
+        <v>65.06121630000001</v>
+      </c>
+      <c r="N81">
+        <v>930.1387837</v>
+      </c>
+      <c r="O81">
+        <v>223.233308088</v>
+      </c>
+      <c r="P81">
+        <v>706.905475612</v>
+      </c>
+      <c r="Q81">
+        <v>896.105475612</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3846006585191222</v>
+      </c>
+      <c r="T81">
+        <v>3.56213194053118</v>
+      </c>
+      <c r="U81">
+        <v>0.0457</v>
+      </c>
+      <c r="V81">
+        <v>0.24</v>
+      </c>
+      <c r="W81">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>15.29636328056166</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1079486796366296</v>
+      </c>
+      <c r="C82">
+        <v>409.2654903048167</v>
+      </c>
+      <c r="D82">
+        <v>1140.545490304817</v>
+      </c>
+      <c r="E82">
+        <v>807.3800000000001</v>
+      </c>
+      <c r="F82">
+        <v>1441.68</v>
+      </c>
+      <c r="G82">
+        <v>710.4</v>
+      </c>
+      <c r="H82">
+        <v>1167.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1184.4</v>
+      </c>
+      <c r="K82">
+        <v>189.2</v>
+      </c>
+      <c r="L82">
+        <v>995.2</v>
+      </c>
+      <c r="M82">
+        <v>65.88477600000002</v>
+      </c>
+      <c r="N82">
+        <v>929.3152240000001</v>
+      </c>
+      <c r="O82">
+        <v>223.03565376</v>
+      </c>
+      <c r="P82">
+        <v>706.2795702400001</v>
+      </c>
+      <c r="Q82">
+        <v>895.4795702400002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4008153981831482</v>
+      </c>
+      <c r="T82">
+        <v>3.729161819282643</v>
+      </c>
+      <c r="U82">
+        <v>0.0457</v>
+      </c>
+      <c r="V82">
+        <v>0.24</v>
+      </c>
+      <c r="W82">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>15.10515873955464</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1076929409842436</v>
+      </c>
+      <c r="C83">
+        <v>391.8621912434096</v>
+      </c>
+      <c r="D83">
+        <v>1141.16319124341</v>
+      </c>
+      <c r="E83">
+        <v>825.4010000000001</v>
+      </c>
+      <c r="F83">
+        <v>1459.701</v>
+      </c>
+      <c r="G83">
+        <v>710.4</v>
+      </c>
+      <c r="H83">
+        <v>1167.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1184.4</v>
+      </c>
+      <c r="K83">
+        <v>189.2</v>
+      </c>
+      <c r="L83">
+        <v>995.2</v>
+      </c>
+      <c r="M83">
+        <v>66.70833570000001</v>
+      </c>
+      <c r="N83">
+        <v>928.4916643</v>
+      </c>
+      <c r="O83">
+        <v>222.837999432</v>
+      </c>
+      <c r="P83">
+        <v>705.6536648680001</v>
+      </c>
+      <c r="Q83">
+        <v>894.8536648680001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4187369525486506</v>
+      </c>
+      <c r="T83">
+        <v>3.913773790534258</v>
+      </c>
+      <c r="U83">
+        <v>0.0457</v>
+      </c>
+      <c r="V83">
+        <v>0.24</v>
+      </c>
+      <c r="W83">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>14.91867529832557</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1074372023318576</v>
+      </c>
+      <c r="C84">
+        <v>374.459561618178</v>
+      </c>
+      <c r="D84">
+        <v>1141.781561618178</v>
+      </c>
+      <c r="E84">
+        <v>843.422</v>
+      </c>
+      <c r="F84">
+        <v>1477.722</v>
+      </c>
+      <c r="G84">
+        <v>710.4</v>
+      </c>
+      <c r="H84">
+        <v>1167.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1184.4</v>
+      </c>
+      <c r="K84">
+        <v>189.2</v>
+      </c>
+      <c r="L84">
+        <v>995.2</v>
+      </c>
+      <c r="M84">
+        <v>67.53189540000001</v>
+      </c>
+      <c r="N84">
+        <v>927.6681046</v>
+      </c>
+      <c r="O84">
+        <v>222.640345104</v>
+      </c>
+      <c r="P84">
+        <v>705.027759496</v>
+      </c>
+      <c r="Q84">
+        <v>894.2277594960001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4386497907325422</v>
+      </c>
+      <c r="T84">
+        <v>4.118898203036054</v>
+      </c>
+      <c r="U84">
+        <v>0.0457</v>
+      </c>
+      <c r="V84">
+        <v>0.24</v>
+      </c>
+      <c r="W84">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>14.73674023371184</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1071814636794715</v>
+      </c>
+      <c r="C85">
+        <v>357.0576025179673</v>
+      </c>
+      <c r="D85">
+        <v>1142.400602517968</v>
+      </c>
+      <c r="E85">
+        <v>861.4430000000002</v>
+      </c>
+      <c r="F85">
+        <v>1495.743</v>
+      </c>
+      <c r="G85">
+        <v>710.4</v>
+      </c>
+      <c r="H85">
+        <v>1167.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1184.4</v>
+      </c>
+      <c r="K85">
+        <v>189.2</v>
+      </c>
+      <c r="L85">
+        <v>995.2</v>
+      </c>
+      <c r="M85">
+        <v>68.35545510000001</v>
+      </c>
+      <c r="N85">
+        <v>926.8445449000001</v>
+      </c>
+      <c r="O85">
+        <v>222.442690776</v>
+      </c>
+      <c r="P85">
+        <v>704.401854124</v>
+      </c>
+      <c r="Q85">
+        <v>893.6018541240001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4609053157615975</v>
+      </c>
+      <c r="T85">
+        <v>4.348154899361591</v>
+      </c>
+      <c r="U85">
+        <v>0.0457</v>
+      </c>
+      <c r="V85">
+        <v>0.24</v>
+      </c>
+      <c r="W85">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>14.55918914655869</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1069257250270855</v>
+      </c>
+      <c r="C86">
+        <v>339.6563150339887</v>
+      </c>
+      <c r="D86">
+        <v>1143.020315033988</v>
+      </c>
+      <c r="E86">
+        <v>879.4639999999999</v>
+      </c>
+      <c r="F86">
+        <v>1513.764</v>
+      </c>
+      <c r="G86">
+        <v>710.4</v>
+      </c>
+      <c r="H86">
+        <v>1167.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1184.4</v>
+      </c>
+      <c r="K86">
+        <v>189.2</v>
+      </c>
+      <c r="L86">
+        <v>995.2</v>
+      </c>
+      <c r="M86">
+        <v>69.1790148</v>
+      </c>
+      <c r="N86">
+        <v>926.0209852</v>
+      </c>
+      <c r="O86">
+        <v>222.245036448</v>
+      </c>
+      <c r="P86">
+        <v>703.775948752</v>
+      </c>
+      <c r="Q86">
+        <v>892.975948752</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4859427814192844</v>
+      </c>
+      <c r="T86">
+        <v>4.606068682727817</v>
+      </c>
+      <c r="U86">
+        <v>0.0457</v>
+      </c>
+      <c r="V86">
+        <v>0.24</v>
+      </c>
+      <c r="W86">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>14.38586546624252</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1066699863746995</v>
+      </c>
+      <c r="C87">
+        <v>322.2557002598192</v>
+      </c>
+      <c r="D87">
+        <v>1143.640700259819</v>
+      </c>
+      <c r="E87">
+        <v>897.4849999999999</v>
+      </c>
+      <c r="F87">
+        <v>1531.785</v>
+      </c>
+      <c r="G87">
+        <v>710.4</v>
+      </c>
+      <c r="H87">
+        <v>1167.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1184.4</v>
+      </c>
+      <c r="K87">
+        <v>189.2</v>
+      </c>
+      <c r="L87">
+        <v>995.2</v>
+      </c>
+      <c r="M87">
+        <v>70.00257449999999</v>
+      </c>
+      <c r="N87">
+        <v>925.1974255</v>
+      </c>
+      <c r="O87">
+        <v>222.04738212</v>
+      </c>
+      <c r="P87">
+        <v>703.1500433800001</v>
+      </c>
+      <c r="Q87">
+        <v>892.35004338</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5143185758313299</v>
+      </c>
+      <c r="T87">
+        <v>4.898370970542876</v>
+      </c>
+      <c r="U87">
+        <v>0.0457</v>
+      </c>
+      <c r="V87">
+        <v>0.24</v>
+      </c>
+      <c r="W87">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>14.21661999016908</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1064142477223134</v>
+      </c>
+      <c r="C88">
+        <v>304.8557592914128</v>
+      </c>
+      <c r="D88">
+        <v>1144.261759291413</v>
+      </c>
+      <c r="E88">
+        <v>915.5059999999999</v>
+      </c>
+      <c r="F88">
+        <v>1549.806</v>
+      </c>
+      <c r="G88">
+        <v>710.4</v>
+      </c>
+      <c r="H88">
+        <v>1167.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1184.4</v>
+      </c>
+      <c r="K88">
+        <v>189.2</v>
+      </c>
+      <c r="L88">
+        <v>995.2</v>
+      </c>
+      <c r="M88">
+        <v>70.8261342</v>
+      </c>
+      <c r="N88">
+        <v>924.3738658000001</v>
+      </c>
+      <c r="O88">
+        <v>221.849727792</v>
+      </c>
+      <c r="P88">
+        <v>702.5241380080001</v>
+      </c>
+      <c r="Q88">
+        <v>891.7241380080002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5467480551593817</v>
+      </c>
+      <c r="T88">
+        <v>5.2324307280458</v>
+      </c>
+      <c r="U88">
+        <v>0.0457</v>
+      </c>
+      <c r="V88">
+        <v>0.24</v>
+      </c>
+      <c r="W88">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>14.05131045539967</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1061585090699274</v>
+      </c>
+      <c r="C89">
+        <v>287.4564932271062</v>
+      </c>
+      <c r="D89">
+        <v>1144.883493227106</v>
+      </c>
+      <c r="E89">
+        <v>933.527</v>
+      </c>
+      <c r="F89">
+        <v>1567.827</v>
+      </c>
+      <c r="G89">
+        <v>710.4</v>
+      </c>
+      <c r="H89">
+        <v>1167.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1184.4</v>
+      </c>
+      <c r="K89">
+        <v>189.2</v>
+      </c>
+      <c r="L89">
+        <v>995.2</v>
+      </c>
+      <c r="M89">
+        <v>71.6496939</v>
+      </c>
+      <c r="N89">
+        <v>923.5503061000001</v>
+      </c>
+      <c r="O89">
+        <v>221.652073464</v>
+      </c>
+      <c r="P89">
+        <v>701.8982326360001</v>
+      </c>
+      <c r="Q89">
+        <v>891.0982326360001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5841666851532878</v>
+      </c>
+      <c r="T89">
+        <v>5.617884294395328</v>
+      </c>
+      <c r="U89">
+        <v>0.0457</v>
+      </c>
+      <c r="V89">
+        <v>0.24</v>
+      </c>
+      <c r="W89">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>13.88980113982036</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1059027704175414</v>
+      </c>
+      <c r="C90">
+        <v>270.057903167623</v>
+      </c>
+      <c r="D90">
+        <v>1145.505903167623</v>
+      </c>
+      <c r="E90">
+        <v>951.548</v>
+      </c>
+      <c r="F90">
+        <v>1585.848</v>
+      </c>
+      <c r="G90">
+        <v>710.4</v>
+      </c>
+      <c r="H90">
+        <v>1167.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1184.4</v>
+      </c>
+      <c r="K90">
+        <v>189.2</v>
+      </c>
+      <c r="L90">
+        <v>995.2</v>
+      </c>
+      <c r="M90">
+        <v>72.47325360000001</v>
+      </c>
+      <c r="N90">
+        <v>922.7267464</v>
+      </c>
+      <c r="O90">
+        <v>221.454419136</v>
+      </c>
+      <c r="P90">
+        <v>701.2723272640001</v>
+      </c>
+      <c r="Q90">
+        <v>890.4723272640001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6278217534795116</v>
+      </c>
+      <c r="T90">
+        <v>6.067580121803111</v>
+      </c>
+      <c r="U90">
+        <v>0.0457</v>
+      </c>
+      <c r="V90">
+        <v>0.24</v>
+      </c>
+      <c r="W90">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>13.73196249050422</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1056470317651554</v>
+      </c>
+      <c r="C91">
+        <v>252.6599902160822</v>
+      </c>
+      <c r="D91">
+        <v>1146.128990216082</v>
+      </c>
+      <c r="E91">
+        <v>969.569</v>
+      </c>
+      <c r="F91">
+        <v>1603.869</v>
+      </c>
+      <c r="G91">
+        <v>710.4</v>
+      </c>
+      <c r="H91">
+        <v>1167.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1184.4</v>
+      </c>
+      <c r="K91">
+        <v>189.2</v>
+      </c>
+      <c r="L91">
+        <v>995.2</v>
+      </c>
+      <c r="M91">
+        <v>73.2968133</v>
+      </c>
+      <c r="N91">
+        <v>921.9031867000001</v>
+      </c>
+      <c r="O91">
+        <v>221.256764808</v>
+      </c>
+      <c r="P91">
+        <v>700.646421892</v>
+      </c>
+      <c r="Q91">
+        <v>889.8464218920001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6794141069559578</v>
+      </c>
+      <c r="T91">
+        <v>6.599038826921398</v>
+      </c>
+      <c r="U91">
+        <v>0.0457</v>
+      </c>
+      <c r="V91">
+        <v>0.24</v>
+      </c>
+      <c r="W91">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>13.57767077712777</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1053912931127693</v>
+      </c>
+      <c r="C92">
+        <v>235.2627554780056</v>
+      </c>
+      <c r="D92">
+        <v>1146.752755478005</v>
+      </c>
+      <c r="E92">
+        <v>987.5899999999999</v>
+      </c>
+      <c r="F92">
+        <v>1621.89</v>
+      </c>
+      <c r="G92">
+        <v>710.4</v>
+      </c>
+      <c r="H92">
+        <v>1167.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1184.4</v>
+      </c>
+      <c r="K92">
+        <v>189.2</v>
+      </c>
+      <c r="L92">
+        <v>995.2</v>
+      </c>
+      <c r="M92">
+        <v>74.120373</v>
+      </c>
+      <c r="N92">
+        <v>921.0796270000001</v>
+      </c>
+      <c r="O92">
+        <v>221.05911048</v>
+      </c>
+      <c r="P92">
+        <v>700.02051652</v>
+      </c>
+      <c r="Q92">
+        <v>889.22051652</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7413249311276935</v>
+      </c>
+      <c r="T92">
+        <v>7.236789273063346</v>
+      </c>
+      <c r="U92">
+        <v>0.0457</v>
+      </c>
+      <c r="V92">
+        <v>0.24</v>
+      </c>
+      <c r="W92">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>13.42680776849302</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1051355544603833</v>
+      </c>
+      <c r="C93">
+        <v>217.8662000613203</v>
+      </c>
+      <c r="D93">
+        <v>1147.37720006132</v>
+      </c>
+      <c r="E93">
+        <v>1005.611</v>
+      </c>
+      <c r="F93">
+        <v>1639.911</v>
+      </c>
+      <c r="G93">
+        <v>710.4</v>
+      </c>
+      <c r="H93">
+        <v>1167.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1184.4</v>
+      </c>
+      <c r="K93">
+        <v>189.2</v>
+      </c>
+      <c r="L93">
+        <v>995.2</v>
+      </c>
+      <c r="M93">
+        <v>74.9439327</v>
+      </c>
+      <c r="N93">
+        <v>920.2560673</v>
+      </c>
+      <c r="O93">
+        <v>220.861456152</v>
+      </c>
+      <c r="P93">
+        <v>699.3946111480001</v>
+      </c>
+      <c r="Q93">
+        <v>888.594611148</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8169937162264813</v>
+      </c>
+      <c r="T93">
+        <v>8.016262040570169</v>
+      </c>
+      <c r="U93">
+        <v>0.0457</v>
+      </c>
+      <c r="V93">
+        <v>0.24</v>
+      </c>
+      <c r="W93">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>13.27926043037771</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1048798158079973</v>
+      </c>
+      <c r="C94">
+        <v>200.4703250763703</v>
+      </c>
+      <c r="D94">
+        <v>1148.00232507637</v>
+      </c>
+      <c r="E94">
+        <v>1023.632</v>
+      </c>
+      <c r="F94">
+        <v>1657.932</v>
+      </c>
+      <c r="G94">
+        <v>710.4</v>
+      </c>
+      <c r="H94">
+        <v>1167.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1184.4</v>
+      </c>
+      <c r="K94">
+        <v>189.2</v>
+      </c>
+      <c r="L94">
+        <v>995.2</v>
+      </c>
+      <c r="M94">
+        <v>75.76749240000001</v>
+      </c>
+      <c r="N94">
+        <v>919.4325076</v>
+      </c>
+      <c r="O94">
+        <v>220.663801824</v>
+      </c>
+      <c r="P94">
+        <v>698.768705776</v>
+      </c>
+      <c r="Q94">
+        <v>887.968705776</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9115796975999666</v>
+      </c>
+      <c r="T94">
+        <v>8.990602999953701</v>
+      </c>
+      <c r="U94">
+        <v>0.0457</v>
+      </c>
+      <c r="V94">
+        <v>0.24</v>
+      </c>
+      <c r="W94">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>13.13492064309099</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1046240771556113</v>
+      </c>
+      <c r="C95">
+        <v>183.0751316359197</v>
+      </c>
+      <c r="D95">
+        <v>1148.62813163592</v>
+      </c>
+      <c r="E95">
+        <v>1041.653</v>
+      </c>
+      <c r="F95">
+        <v>1675.953</v>
+      </c>
+      <c r="G95">
+        <v>710.4</v>
+      </c>
+      <c r="H95">
+        <v>1167.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1184.4</v>
+      </c>
+      <c r="K95">
+        <v>189.2</v>
+      </c>
+      <c r="L95">
+        <v>995.2</v>
+      </c>
+      <c r="M95">
+        <v>76.59105210000001</v>
+      </c>
+      <c r="N95">
+        <v>918.6089479</v>
+      </c>
+      <c r="O95">
+        <v>220.466147496</v>
+      </c>
+      <c r="P95">
+        <v>698.142800404</v>
+      </c>
+      <c r="Q95">
+        <v>887.3428004039999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.033190245080162</v>
+      </c>
+      <c r="T95">
+        <v>10.24332709058967</v>
+      </c>
+      <c r="U95">
+        <v>0.0457</v>
+      </c>
+      <c r="V95">
+        <v>0.24</v>
+      </c>
+      <c r="W95">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>12.9936849372513</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1055113785032252</v>
+      </c>
+      <c r="C96">
+        <v>162.8857739022758</v>
+      </c>
+      <c r="D96">
+        <v>1146.459773902276</v>
+      </c>
+      <c r="E96">
+        <v>1059.674</v>
+      </c>
+      <c r="F96">
+        <v>1693.974</v>
+      </c>
+      <c r="G96">
+        <v>710.4</v>
+      </c>
+      <c r="H96">
+        <v>1167.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1184.4</v>
+      </c>
+      <c r="K96">
+        <v>189.2</v>
+      </c>
+      <c r="L96">
+        <v>995.2</v>
+      </c>
+      <c r="M96">
+        <v>80.12497019999999</v>
+      </c>
+      <c r="N96">
+        <v>915.0750298</v>
+      </c>
+      <c r="O96">
+        <v>219.618007152</v>
+      </c>
+      <c r="P96">
+        <v>695.457022648</v>
+      </c>
+      <c r="Q96">
+        <v>884.6570226480001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.195337641720422</v>
+      </c>
+      <c r="T96">
+        <v>11.91362587810429</v>
+      </c>
+      <c r="U96">
+        <v>0.0473</v>
+      </c>
+      <c r="V96">
+        <v>0.24</v>
+      </c>
+      <c r="W96">
+        <v>0.035948</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>12.4205974431676</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1052677998508392</v>
+      </c>
+      <c r="C97">
+        <v>145.4592077207574</v>
+      </c>
+      <c r="D97">
+        <v>1147.054207720758</v>
+      </c>
+      <c r="E97">
+        <v>1077.695</v>
+      </c>
+      <c r="F97">
+        <v>1711.995</v>
+      </c>
+      <c r="G97">
+        <v>710.4</v>
+      </c>
+      <c r="H97">
+        <v>1167.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1184.4</v>
+      </c>
+      <c r="K97">
+        <v>189.2</v>
+      </c>
+      <c r="L97">
+        <v>995.2</v>
+      </c>
+      <c r="M97">
+        <v>80.97736350000001</v>
+      </c>
+      <c r="N97">
+        <v>914.2226365</v>
+      </c>
+      <c r="O97">
+        <v>219.41343276</v>
+      </c>
+      <c r="P97">
+        <v>694.80920374</v>
+      </c>
+      <c r="Q97">
+        <v>884.00920374</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.422343997016786</v>
+      </c>
+      <c r="T97">
+        <v>14.25204418062477</v>
+      </c>
+      <c r="U97">
+        <v>0.0473</v>
+      </c>
+      <c r="V97">
+        <v>0.24</v>
+      </c>
+      <c r="W97">
+        <v>0.035948</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>12.28985431218689</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1050242211984532</v>
+      </c>
+      <c r="C98">
+        <v>128.0332582811063</v>
+      </c>
+      <c r="D98">
+        <v>1147.649258281106</v>
+      </c>
+      <c r="E98">
+        <v>1095.716</v>
+      </c>
+      <c r="F98">
+        <v>1730.016</v>
+      </c>
+      <c r="G98">
+        <v>710.4</v>
+      </c>
+      <c r="H98">
+        <v>1167.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1184.4</v>
+      </c>
+      <c r="K98">
+        <v>189.2</v>
+      </c>
+      <c r="L98">
+        <v>995.2</v>
+      </c>
+      <c r="M98">
+        <v>81.8297568</v>
+      </c>
+      <c r="N98">
+        <v>913.3702432</v>
+      </c>
+      <c r="O98">
+        <v>219.208858368</v>
+      </c>
+      <c r="P98">
+        <v>694.1613848320001</v>
+      </c>
+      <c r="Q98">
+        <v>883.3613848320001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.762853529961327</v>
+      </c>
+      <c r="T98">
+        <v>17.75967163440544</v>
+      </c>
+      <c r="U98">
+        <v>0.0473</v>
+      </c>
+      <c r="V98">
+        <v>0.24</v>
+      </c>
+      <c r="W98">
+        <v>0.035948</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>12.16183499643494</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1047806425460672</v>
+      </c>
+      <c r="C99">
+        <v>110.607926543651</v>
+      </c>
+      <c r="D99">
+        <v>1148.244926543651</v>
+      </c>
+      <c r="E99">
+        <v>1113.737</v>
+      </c>
+      <c r="F99">
+        <v>1748.037</v>
+      </c>
+      <c r="G99">
+        <v>710.4</v>
+      </c>
+      <c r="H99">
+        <v>1167.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1184.4</v>
+      </c>
+      <c r="K99">
+        <v>189.2</v>
+      </c>
+      <c r="L99">
+        <v>995.2</v>
+      </c>
+      <c r="M99">
+        <v>82.68215009999999</v>
+      </c>
+      <c r="N99">
+        <v>912.5178499000001</v>
+      </c>
+      <c r="O99">
+        <v>219.004283976</v>
+      </c>
+      <c r="P99">
+        <v>693.5135659240001</v>
+      </c>
+      <c r="Q99">
+        <v>882.713565924</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.330369418202237</v>
+      </c>
+      <c r="T99">
+        <v>23.60571739070661</v>
+      </c>
+      <c r="U99">
+        <v>0.0473</v>
+      </c>
+      <c r="V99">
+        <v>0.24</v>
+      </c>
+      <c r="W99">
+        <v>0.035948</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>12.03645525420366</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1045370638936811</v>
+      </c>
+      <c r="C100">
+        <v>93.18321347071492</v>
+      </c>
+      <c r="D100">
+        <v>1148.841213470715</v>
+      </c>
+      <c r="E100">
+        <v>1131.758</v>
+      </c>
+      <c r="F100">
+        <v>1766.058</v>
+      </c>
+      <c r="G100">
+        <v>710.4</v>
+      </c>
+      <c r="H100">
+        <v>1167.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1184.4</v>
+      </c>
+      <c r="K100">
+        <v>189.2</v>
+      </c>
+      <c r="L100">
+        <v>995.2</v>
+      </c>
+      <c r="M100">
+        <v>83.53454339999999</v>
+      </c>
+      <c r="N100">
+        <v>911.6654566000001</v>
+      </c>
+      <c r="O100">
+        <v>218.799709584</v>
+      </c>
+      <c r="P100">
+        <v>692.8657470160001</v>
+      </c>
+      <c r="Q100">
+        <v>882.0657470160002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.465401194684052</v>
+      </c>
+      <c r="T100">
+        <v>35.29780890330893</v>
+      </c>
+      <c r="U100">
+        <v>0.0473</v>
+      </c>
+      <c r="V100">
+        <v>0.24</v>
+      </c>
+      <c r="W100">
+        <v>0.035948</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>11.91363428222198</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1042934852412951</v>
+      </c>
+      <c r="C101">
+        <v>75.75912002662176</v>
+      </c>
+      <c r="D101">
+        <v>1149.438120026622</v>
+      </c>
+      <c r="E101">
+        <v>1149.779</v>
+      </c>
+      <c r="F101">
+        <v>1784.079</v>
+      </c>
+      <c r="G101">
+        <v>710.4</v>
+      </c>
+      <c r="H101">
+        <v>1167.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1184.4</v>
+      </c>
+      <c r="K101">
+        <v>189.2</v>
+      </c>
+      <c r="L101">
+        <v>995.2</v>
+      </c>
+      <c r="M101">
+        <v>84.38693670000001</v>
+      </c>
+      <c r="N101">
+        <v>910.8130633000001</v>
+      </c>
+      <c r="O101">
+        <v>218.595135192</v>
+      </c>
+      <c r="P101">
+        <v>692.217928108</v>
+      </c>
+      <c r="Q101">
+        <v>881.4179281080001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.870496524129503</v>
+      </c>
+      <c r="T101">
+        <v>70.37408344111593</v>
+      </c>
+      <c r="U101">
+        <v>0.0473</v>
+      </c>
+      <c r="V101">
+        <v>0.24</v>
+      </c>
+      <c r="W101">
+        <v>0.035948</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>11.79329454199752</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
